--- a/doc/cmu_soe_cfg.xlsx
+++ b/doc/cmu_soe_cfg.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2078" uniqueCount="533">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2078" uniqueCount="534">
   <si>
     <t>id</t>
   </si>
@@ -1278,6 +1278,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>KM</t>
     </r>
     <r>
@@ -1384,6 +1389,19 @@
     <t>电压压差,U16,0.0001,0,V</t>
   </si>
   <si>
+    <r>
+      <t>门限电压</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>,U16,0.0001,0,V</t>
+    </r>
+  </si>
+  <si>
     <t>单体电压,U16,0.0001,0,V</t>
   </si>
   <si>
@@ -1526,6 +1544,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>断线</t>
     </r>
     <r>
@@ -1583,6 +1606,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>系统上次的状态</t>
     </r>
     <r>
@@ -1605,6 +1633,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>线圈</t>
     </r>
     <r>
@@ -1641,6 +1674,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>CMU</t>
     </r>
     <r>
@@ -1703,6 +1741,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>KM</t>
     </r>
     <r>
@@ -1746,6 +1789,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>KMR</t>
     </r>
     <r>
@@ -1768,6 +1816,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>变位前状态</t>
     </r>
     <r>
@@ -1781,6 +1834,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>变位后状态</t>
     </r>
     <r>
@@ -1801,10 +1859,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -1819,16 +1877,38 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1841,21 +1921,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1864,6 +1930,13 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1900,6 +1973,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
@@ -1924,8 +2005,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1938,32 +2020,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1978,19 +2036,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2002,7 +2054,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2014,13 +2078,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2032,13 +2090,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2050,49 +2108,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2110,13 +2132,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2128,37 +2216,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2173,21 +2231,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
@@ -2198,50 +2241,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2269,55 +2268,108 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2326,101 +2378,107 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -8176,7 +8234,7 @@
       <c r="D127" t="s">
         <v>340</v>
       </c>
-      <c r="E127" s="2" t="s">
+      <c r="E127" s="1" t="s">
         <v>341</v>
       </c>
       <c r="F127" t="s">
@@ -10881,7 +10939,7 @@
       <c r="D194" t="s">
         <v>327</v>
       </c>
-      <c r="E194" s="2" t="s">
+      <c r="E194" s="1" t="s">
         <v>416</v>
       </c>
       <c r="F194" t="s">
@@ -11200,7 +11258,7 @@
       <c r="D202" t="s">
         <v>343</v>
       </c>
-      <c r="E202" s="1" t="s">
+      <c r="E202" s="2" t="s">
         <v>420</v>
       </c>
       <c r="F202" t="s">
@@ -11798,8 +11856,8 @@
       <c r="G6" t="s">
         <v>446</v>
       </c>
-      <c r="H6" t="s">
-        <v>444</v>
+      <c r="H6" s="1" t="s">
+        <v>447</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -11848,10 +11906,10 @@
         <v>50</v>
       </c>
       <c r="G8" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H8" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -11874,10 +11932,10 @@
         <v>56</v>
       </c>
       <c r="G9" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H9" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -11900,10 +11958,10 @@
         <v>60</v>
       </c>
       <c r="G10" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H10" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -11926,10 +11984,10 @@
         <v>60</v>
       </c>
       <c r="G11" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H11" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -11952,10 +12010,10 @@
         <v>69</v>
       </c>
       <c r="G12" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H12" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -11978,10 +12036,10 @@
         <v>69</v>
       </c>
       <c r="G13" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H13" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -12004,10 +12062,10 @@
         <v>77</v>
       </c>
       <c r="G14" t="s">
+        <v>454</v>
+      </c>
+      <c r="H14" t="s">
         <v>453</v>
-      </c>
-      <c r="H14" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -12030,10 +12088,10 @@
         <v>77</v>
       </c>
       <c r="G15" t="s">
+        <v>454</v>
+      </c>
+      <c r="H15" t="s">
         <v>453</v>
-      </c>
-      <c r="H15" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -12056,10 +12114,10 @@
         <v>85</v>
       </c>
       <c r="G16" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H16" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -12082,10 +12140,10 @@
         <v>85</v>
       </c>
       <c r="G17" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H17" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -12108,10 +12166,10 @@
         <v>93</v>
       </c>
       <c r="G18" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H18" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -12134,10 +12192,10 @@
         <v>98</v>
       </c>
       <c r="G19" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H19" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -12160,10 +12218,10 @@
         <v>103</v>
       </c>
       <c r="G20" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H20" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -12186,10 +12244,10 @@
         <v>103</v>
       </c>
       <c r="G21" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H21" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -12212,10 +12270,10 @@
         <v>111</v>
       </c>
       <c r="G22" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H22" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -12234,12 +12292,11 @@
       <c r="E23" t="s">
         <v>115</v>
       </c>
-      <c r="F23"/>
       <c r="G23" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H23" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -12258,12 +12315,11 @@
       <c r="E24" t="s">
         <v>121</v>
       </c>
-      <c r="F24"/>
       <c r="G24" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H24" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -12282,12 +12338,11 @@
       <c r="E25" t="s">
         <v>125</v>
       </c>
-      <c r="F25"/>
       <c r="G25" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H25" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -12306,12 +12361,11 @@
       <c r="E26" t="s">
         <v>129</v>
       </c>
-      <c r="F26"/>
       <c r="G26" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H26" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -12330,12 +12384,11 @@
       <c r="E27" t="s">
         <v>133</v>
       </c>
-      <c r="F27"/>
       <c r="G27" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H27" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -12354,12 +12407,11 @@
       <c r="E28" t="s">
         <v>138</v>
       </c>
-      <c r="F28"/>
       <c r="G28" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H28" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -12378,12 +12430,11 @@
       <c r="E29" t="s">
         <v>141</v>
       </c>
-      <c r="F29"/>
       <c r="G29" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H29" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -12402,12 +12453,11 @@
       <c r="E30" t="s">
         <v>144</v>
       </c>
-      <c r="F30"/>
       <c r="G30" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H30" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -12426,12 +12476,11 @@
       <c r="E31" t="s">
         <v>148</v>
       </c>
-      <c r="F31"/>
       <c r="G31" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H31" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -12450,12 +12499,11 @@
       <c r="E32" t="s">
         <v>151</v>
       </c>
-      <c r="F32"/>
       <c r="G32" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H32" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -12474,12 +12522,11 @@
       <c r="E33" t="s">
         <v>156</v>
       </c>
-      <c r="F33"/>
       <c r="G33" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H33" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -12498,12 +12545,11 @@
       <c r="E34" t="s">
         <v>159</v>
       </c>
-      <c r="F34"/>
       <c r="G34" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H34" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -12522,12 +12568,11 @@
       <c r="E35" t="s">
         <v>163</v>
       </c>
-      <c r="F35"/>
       <c r="G35" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H35" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -12550,10 +12595,10 @@
         <v>167</v>
       </c>
       <c r="G36" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H36" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -12576,10 +12621,10 @@
         <v>167</v>
       </c>
       <c r="G37" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H37" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -12602,10 +12647,10 @@
         <v>167</v>
       </c>
       <c r="G38" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H38" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -12628,10 +12673,10 @@
         <v>167</v>
       </c>
       <c r="G39" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H39" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -12654,10 +12699,10 @@
         <v>167</v>
       </c>
       <c r="G40" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H40" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -12680,10 +12725,10 @@
         <v>167</v>
       </c>
       <c r="G41" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H41" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -12706,10 +12751,10 @@
         <v>187</v>
       </c>
       <c r="G42" t="s">
+        <v>469</v>
+      </c>
+      <c r="H42" t="s">
         <v>468</v>
-      </c>
-      <c r="H42" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -12732,10 +12777,10 @@
         <v>187</v>
       </c>
       <c r="G43" t="s">
+        <v>469</v>
+      </c>
+      <c r="H43" t="s">
         <v>468</v>
-      </c>
-      <c r="H43" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -12754,12 +12799,11 @@
       <c r="E44" t="s">
         <v>194</v>
       </c>
-      <c r="F44"/>
       <c r="G44" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H44" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -12778,12 +12822,11 @@
       <c r="E45" t="s">
         <v>198</v>
       </c>
-      <c r="F45"/>
       <c r="G45" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H45" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -12802,12 +12845,11 @@
       <c r="E46" t="s">
         <v>202</v>
       </c>
-      <c r="F46"/>
       <c r="G46" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H46" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -12826,12 +12868,11 @@
       <c r="E47" t="s">
         <v>206</v>
       </c>
-      <c r="F47"/>
       <c r="G47" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H47" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -12850,12 +12891,11 @@
       <c r="E48" t="s">
         <v>209</v>
       </c>
-      <c r="F48"/>
       <c r="G48" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H48" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -12874,12 +12914,11 @@
       <c r="E49" t="s">
         <v>212</v>
       </c>
-      <c r="F49"/>
       <c r="G49" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H49" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="50" spans="1:8">
@@ -12898,12 +12937,11 @@
       <c r="E50" t="s">
         <v>216</v>
       </c>
-      <c r="F50"/>
       <c r="G50" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H50" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="51" spans="1:8">
@@ -12922,12 +12960,11 @@
       <c r="E51" t="s">
         <v>219</v>
       </c>
-      <c r="F51"/>
       <c r="G51" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H51" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="52" spans="1:8">
@@ -12950,10 +12987,10 @@
         <v>223</v>
       </c>
       <c r="G52" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H52" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="53" spans="1:8">
@@ -12969,15 +13006,14 @@
       <c r="D53">
         <v>0</v>
       </c>
-      <c r="E53" s="1" t="s">
-        <v>474</v>
-      </c>
-      <c r="F53"/>
+      <c r="E53" s="2" t="s">
+        <v>475</v>
+      </c>
       <c r="G53" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H53" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="54" spans="1:8">
@@ -12996,12 +13032,11 @@
       <c r="E54" t="s">
         <v>230</v>
       </c>
-      <c r="F54"/>
-      <c r="G54" s="1" t="s">
-        <v>475</v>
+      <c r="G54" s="2" t="s">
+        <v>476</v>
       </c>
       <c r="H54" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="55" spans="1:8">
@@ -13017,15 +13052,14 @@
       <c r="D55">
         <v>0</v>
       </c>
-      <c r="E55" s="1" t="s">
-        <v>476</v>
-      </c>
-      <c r="F55"/>
+      <c r="E55" s="2" t="s">
+        <v>477</v>
+      </c>
       <c r="G55" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H55" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="56" spans="1:8">
@@ -13044,12 +13078,11 @@
       <c r="E56" t="s">
         <v>238</v>
       </c>
-      <c r="F56"/>
       <c r="G56" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H56" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="57" spans="1:8">
@@ -13068,12 +13101,11 @@
       <c r="E57" t="s">
         <v>241</v>
       </c>
-      <c r="F57"/>
       <c r="G57" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H57" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="58" spans="1:8">
@@ -13092,12 +13124,11 @@
       <c r="E58" t="s">
         <v>245</v>
       </c>
-      <c r="F58"/>
       <c r="G58" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H58" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="59" spans="1:8">
@@ -13120,10 +13151,10 @@
         <v>249</v>
       </c>
       <c r="G59" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H59" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="60" spans="1:8">
@@ -13142,12 +13173,11 @@
       <c r="E60" t="s">
         <v>252</v>
       </c>
-      <c r="F60"/>
       <c r="G60" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H60" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="61" spans="1:8">
@@ -13164,14 +13194,13 @@
         <v>0</v>
       </c>
       <c r="E61" t="s">
-        <v>479</v>
-      </c>
-      <c r="F61"/>
+        <v>480</v>
+      </c>
       <c r="G61" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H61" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="62" spans="1:8">
@@ -13190,12 +13219,11 @@
       <c r="E62" t="s">
         <v>331</v>
       </c>
-      <c r="F62"/>
       <c r="G62" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H62" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="63" spans="1:8">
@@ -13214,12 +13242,11 @@
       <c r="E63" t="s">
         <v>333</v>
       </c>
-      <c r="F63"/>
       <c r="G63" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H63" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="64" spans="1:8">
@@ -13238,12 +13265,11 @@
       <c r="E64" t="s">
         <v>335</v>
       </c>
-      <c r="F64"/>
       <c r="G64" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H64" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="65" spans="1:8">
@@ -13262,12 +13288,11 @@
       <c r="E65" t="s">
         <v>337</v>
       </c>
-      <c r="F65"/>
       <c r="G65" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H65" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="66" spans="1:8">
@@ -13286,12 +13311,11 @@
       <c r="E66" t="s">
         <v>339</v>
       </c>
-      <c r="F66"/>
       <c r="G66" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H66" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="67" spans="1:8">
@@ -13308,14 +13332,13 @@
         <v>0</v>
       </c>
       <c r="E67" t="s">
-        <v>483</v>
-      </c>
-      <c r="F67"/>
+        <v>484</v>
+      </c>
       <c r="G67" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H67" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -13332,13 +13355,13 @@
         <v>0</v>
       </c>
       <c r="E68" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="G68" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H68" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -13355,14 +13378,13 @@
         <v>0</v>
       </c>
       <c r="E69" t="s">
-        <v>487</v>
-      </c>
-      <c r="F69"/>
+        <v>488</v>
+      </c>
       <c r="G69" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H69" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="70" spans="1:8">
@@ -13385,10 +13407,10 @@
         <v>299</v>
       </c>
       <c r="G70" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H70" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="71" spans="1:8">
@@ -13407,12 +13429,11 @@
       <c r="E71" t="s">
         <v>351</v>
       </c>
-      <c r="F71"/>
       <c r="G71" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H71" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="72" spans="1:8">
@@ -13431,12 +13452,11 @@
       <c r="E72" t="s">
         <v>354</v>
       </c>
-      <c r="F72"/>
       <c r="G72" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H72" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="73" spans="1:8">
@@ -13455,12 +13475,11 @@
       <c r="E73" t="s">
         <v>356</v>
       </c>
-      <c r="F73"/>
       <c r="G73" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H73" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -13479,12 +13498,11 @@
       <c r="E74" t="s">
         <v>358</v>
       </c>
-      <c r="F74"/>
       <c r="G74" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H74" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="75" spans="1:8">
@@ -13607,12 +13625,11 @@
       <c r="E79" t="s">
         <v>364</v>
       </c>
-      <c r="F79"/>
       <c r="G79" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H79" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="80" spans="1:8">
@@ -13631,12 +13648,11 @@
       <c r="E80" t="s">
         <v>365</v>
       </c>
-      <c r="F80"/>
       <c r="G80" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H80" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="81" spans="1:8">
@@ -13659,10 +13675,10 @@
         <v>366</v>
       </c>
       <c r="G81" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H81" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="82" spans="1:8">
@@ -13681,9 +13697,8 @@
       <c r="E82" t="s">
         <v>55</v>
       </c>
-      <c r="F82"/>
       <c r="G82" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H82" t="s">
         <v>443</v>
@@ -13709,10 +13724,10 @@
         <v>60</v>
       </c>
       <c r="G83" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H83" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="84" spans="1:8">
@@ -13735,10 +13750,10 @@
         <v>60</v>
       </c>
       <c r="G84" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H84" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="85" spans="1:8">
@@ -13761,10 +13776,10 @@
         <v>69</v>
       </c>
       <c r="G85" t="s">
+        <v>452</v>
+      </c>
+      <c r="H85" t="s">
         <v>451</v>
-      </c>
-      <c r="H85" t="s">
-        <v>450</v>
       </c>
     </row>
     <row r="86" spans="1:8">
@@ -13787,10 +13802,10 @@
         <v>69</v>
       </c>
       <c r="G86" t="s">
+        <v>452</v>
+      </c>
+      <c r="H86" t="s">
         <v>451</v>
-      </c>
-      <c r="H86" t="s">
-        <v>450</v>
       </c>
     </row>
     <row r="87" spans="1:8">
@@ -13809,12 +13824,11 @@
       <c r="E87" t="s">
         <v>375</v>
       </c>
-      <c r="F87"/>
       <c r="G87" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H87" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="88" spans="1:8">
@@ -13833,12 +13847,11 @@
       <c r="E88" t="s">
         <v>376</v>
       </c>
-      <c r="F88"/>
       <c r="G88" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H88" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="89" spans="1:8">
@@ -13857,12 +13870,11 @@
       <c r="E89" t="s">
         <v>377</v>
       </c>
-      <c r="F89"/>
       <c r="G89" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H89" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="90" spans="1:8">
@@ -13881,12 +13893,11 @@
       <c r="E90" t="s">
         <v>378</v>
       </c>
-      <c r="F90"/>
       <c r="G90" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H90" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="91" spans="1:8">
@@ -13905,14 +13916,14 @@
       <c r="E91" t="s">
         <v>92</v>
       </c>
-      <c r="F91" s="2" t="s">
-        <v>494</v>
+      <c r="F91" s="1" t="s">
+        <v>495</v>
       </c>
       <c r="G91" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H91" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="92" spans="1:8">
@@ -13931,12 +13942,11 @@
       <c r="E92" t="s">
         <v>97</v>
       </c>
-      <c r="F92"/>
       <c r="G92" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H92" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="93" spans="1:8">
@@ -13959,10 +13969,10 @@
         <v>103</v>
       </c>
       <c r="G93" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H93" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="94" spans="1:8">
@@ -13985,10 +13995,10 @@
         <v>103</v>
       </c>
       <c r="G94" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H94" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="95" spans="1:8">
@@ -14007,12 +14017,11 @@
       <c r="E95" t="s">
         <v>110</v>
       </c>
-      <c r="F95"/>
       <c r="G95" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H95" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="96" spans="1:8">
@@ -14031,12 +14040,11 @@
       <c r="E96" t="s">
         <v>115</v>
       </c>
-      <c r="F96"/>
       <c r="G96" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H96" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="97" spans="1:8">
@@ -14055,12 +14063,11 @@
       <c r="E97" t="s">
         <v>121</v>
       </c>
-      <c r="F97"/>
       <c r="G97" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H97" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="98" spans="1:8">
@@ -14079,12 +14086,11 @@
       <c r="E98" t="s">
         <v>125</v>
       </c>
-      <c r="F98"/>
       <c r="G98" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H98" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="99" spans="1:8">
@@ -14103,12 +14109,11 @@
       <c r="E99" t="s">
         <v>129</v>
       </c>
-      <c r="F99"/>
       <c r="G99" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H99" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="100" spans="1:8">
@@ -14127,12 +14132,11 @@
       <c r="E100" t="s">
         <v>133</v>
       </c>
-      <c r="F100"/>
       <c r="G100" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H100" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="101" spans="1:8">
@@ -14151,12 +14155,11 @@
       <c r="E101" t="s">
         <v>138</v>
       </c>
-      <c r="F101"/>
       <c r="G101" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H101" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="102" spans="1:8">
@@ -14175,12 +14178,11 @@
       <c r="E102" t="s">
         <v>141</v>
       </c>
-      <c r="F102"/>
       <c r="G102" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H102" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="103" spans="1:8">
@@ -14199,12 +14201,11 @@
       <c r="E103" t="s">
         <v>144</v>
       </c>
-      <c r="F103"/>
       <c r="G103" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H103" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="104" spans="1:8">
@@ -14223,12 +14224,11 @@
       <c r="E104" t="s">
         <v>148</v>
       </c>
-      <c r="F104"/>
       <c r="G104" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H104" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="105" spans="1:8">
@@ -14247,12 +14247,11 @@
       <c r="E105" t="s">
         <v>151</v>
       </c>
-      <c r="F105"/>
       <c r="G105" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H105" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="106" spans="1:8">
@@ -14271,12 +14270,11 @@
       <c r="E106" t="s">
         <v>156</v>
       </c>
-      <c r="F106"/>
       <c r="G106" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H106" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="107" spans="1:8">
@@ -14295,12 +14293,11 @@
       <c r="E107" t="s">
         <v>159</v>
       </c>
-      <c r="F107"/>
       <c r="G107" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H107" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="108" spans="1:8">
@@ -14319,12 +14316,11 @@
       <c r="E108" t="s">
         <v>163</v>
       </c>
-      <c r="F108"/>
       <c r="G108" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H108" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="109" spans="1:9">
@@ -14343,14 +14339,14 @@
       <c r="E109" t="s">
         <v>166</v>
       </c>
-      <c r="F109" s="2" t="s">
-        <v>504</v>
+      <c r="F109" s="1" t="s">
+        <v>505</v>
       </c>
       <c r="G109" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H109" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="I109" t="s">
         <v>397</v>
@@ -14372,14 +14368,14 @@
       <c r="E110" t="s">
         <v>170</v>
       </c>
-      <c r="F110" s="2" t="s">
-        <v>507</v>
+      <c r="F110" s="1" t="s">
+        <v>508</v>
       </c>
       <c r="G110" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H110" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="I110" t="s">
         <v>399</v>
@@ -14401,14 +14397,14 @@
       <c r="E111" t="s">
         <v>174</v>
       </c>
-      <c r="F111" s="2" t="s">
+      <c r="F111" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="G111" t="s">
+        <v>506</v>
+      </c>
+      <c r="H111" t="s">
         <v>507</v>
-      </c>
-      <c r="G111" t="s">
-        <v>505</v>
-      </c>
-      <c r="H111" t="s">
-        <v>506</v>
       </c>
       <c r="I111" t="s">
         <v>400</v>
@@ -14430,14 +14426,14 @@
       <c r="E112" t="s">
         <v>177</v>
       </c>
-      <c r="F112" s="2" t="s">
-        <v>507</v>
+      <c r="F112" s="1" t="s">
+        <v>508</v>
       </c>
       <c r="G112" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H112" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="I112" t="s">
         <v>401</v>
@@ -14463,10 +14459,10 @@
         <v>31</v>
       </c>
       <c r="G113" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H113" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="114" spans="1:8">
@@ -14489,10 +14485,10 @@
         <v>19</v>
       </c>
       <c r="G114" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H114" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="115" spans="1:8">
@@ -14511,12 +14507,11 @@
       <c r="E115" t="s">
         <v>404</v>
       </c>
-      <c r="F115"/>
       <c r="G115" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H115" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="116" spans="1:8">
@@ -14535,12 +14530,11 @@
       <c r="E116" t="s">
         <v>405</v>
       </c>
-      <c r="F116"/>
       <c r="G116" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H116" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="117" spans="1:8">
@@ -14559,14 +14553,14 @@
       <c r="E117" t="s">
         <v>194</v>
       </c>
-      <c r="F117" s="2" t="s">
-        <v>511</v>
+      <c r="F117" s="1" t="s">
+        <v>512</v>
       </c>
       <c r="G117" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H117" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="118" spans="1:8">
@@ -14585,14 +14579,14 @@
       <c r="E118" t="s">
         <v>198</v>
       </c>
-      <c r="F118" s="2" t="s">
-        <v>511</v>
+      <c r="F118" s="1" t="s">
+        <v>512</v>
       </c>
       <c r="G118" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H118" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="119" spans="1:8">
@@ -14611,14 +14605,14 @@
       <c r="E119" t="s">
         <v>202</v>
       </c>
-      <c r="F119" s="2" t="s">
-        <v>511</v>
+      <c r="F119" s="1" t="s">
+        <v>512</v>
       </c>
       <c r="G119" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H119" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="120" spans="1:8">
@@ -14637,14 +14631,14 @@
       <c r="E120" t="s">
         <v>206</v>
       </c>
-      <c r="F120" s="2" t="s">
-        <v>511</v>
+      <c r="F120" s="1" t="s">
+        <v>512</v>
       </c>
       <c r="G120" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H120" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="121" spans="1:8">
@@ -14663,14 +14657,14 @@
       <c r="E121" t="s">
         <v>209</v>
       </c>
-      <c r="F121" s="2" t="s">
-        <v>511</v>
+      <c r="F121" s="1" t="s">
+        <v>512</v>
       </c>
       <c r="G121" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H121" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="122" spans="1:8">
@@ -14693,10 +14687,10 @@
         <v>303</v>
       </c>
       <c r="G122" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H122" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="123" spans="1:8">
@@ -14719,10 +14713,10 @@
         <v>303</v>
       </c>
       <c r="G123" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H123" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="124" spans="1:8">
@@ -14741,12 +14735,11 @@
       <c r="E124" t="s">
         <v>219</v>
       </c>
-      <c r="F124"/>
       <c r="G124" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H124" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="125" spans="1:8">
@@ -14765,12 +14758,11 @@
       <c r="E125" t="s">
         <v>222</v>
       </c>
-      <c r="F125"/>
       <c r="G125" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H125" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="126" spans="1:8">
@@ -14786,14 +14778,14 @@
       <c r="D126">
         <v>0</v>
       </c>
-      <c r="E126" s="1" t="s">
-        <v>517</v>
+      <c r="E126" s="2" t="s">
+        <v>518</v>
       </c>
       <c r="G126" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H126" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="127" spans="1:8">
@@ -14812,12 +14804,11 @@
       <c r="E127" t="s">
         <v>230</v>
       </c>
-      <c r="F127"/>
       <c r="G127" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H127" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="128" spans="1:8">
@@ -14836,12 +14827,11 @@
       <c r="E128" t="s">
         <v>310</v>
       </c>
-      <c r="F128"/>
       <c r="G128" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H128" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="129" spans="1:8">
@@ -14864,10 +14854,10 @@
         <v>411</v>
       </c>
       <c r="G129" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H129" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="130" spans="1:9">
@@ -14887,14 +14877,13 @@
         <v>316</v>
       </c>
       <c r="F130" t="s">
-        <v>519</v>
-      </c>
-      <c r="G130"/>
+        <v>520</v>
+      </c>
       <c r="H130" t="s">
-        <v>519</v>
-      </c>
-      <c r="I130" s="1" t="s">
         <v>520</v>
+      </c>
+      <c r="I130" s="2" t="s">
+        <v>521</v>
       </c>
     </row>
     <row r="131" spans="1:8">
@@ -14913,12 +14902,11 @@
       <c r="E131" t="s">
         <v>320</v>
       </c>
-      <c r="F131"/>
       <c r="G131" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H131" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="132" spans="1:8">
@@ -14937,12 +14925,11 @@
       <c r="E132" t="s">
         <v>323</v>
       </c>
-      <c r="F132"/>
       <c r="G132" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H132" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="133" spans="1:8">
@@ -14965,10 +14952,10 @@
         <v>415</v>
       </c>
       <c r="G133" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H133" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="134" spans="1:8">
@@ -14984,15 +14971,14 @@
       <c r="D134">
         <v>0</v>
       </c>
-      <c r="E134" s="2" t="s">
+      <c r="E134" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="F134"/>
       <c r="G134" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H134" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="135" spans="1:8">
@@ -15015,10 +15001,10 @@
         <v>415</v>
       </c>
       <c r="G135" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H135" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="136" spans="1:8">
@@ -15041,10 +15027,10 @@
         <v>415</v>
       </c>
       <c r="G136" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H136" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="137" spans="1:8">
@@ -15067,10 +15053,10 @@
         <v>103</v>
       </c>
       <c r="G137" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H137" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="138" spans="1:8">
@@ -15093,10 +15079,10 @@
         <v>103</v>
       </c>
       <c r="G138" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H138" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="139" spans="1:8">
@@ -15115,12 +15101,11 @@
       <c r="E139" t="s">
         <v>339</v>
       </c>
-      <c r="F139"/>
       <c r="G139" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H139" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="140" spans="1:8">
@@ -15139,12 +15124,11 @@
       <c r="E140" t="s">
         <v>341</v>
       </c>
-      <c r="F140"/>
       <c r="G140" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H140" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="141" spans="1:8">
@@ -15163,12 +15147,11 @@
       <c r="E141" t="s">
         <v>321</v>
       </c>
-      <c r="F141"/>
       <c r="G141" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H141" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="142" spans="1:8">
@@ -15184,17 +15167,17 @@
       <c r="D142">
         <v>0</v>
       </c>
-      <c r="E142" s="1" t="s">
-        <v>523</v>
+      <c r="E142" s="2" t="s">
+        <v>524</v>
       </c>
       <c r="F142" t="s">
         <v>421</v>
       </c>
       <c r="G142" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H142" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="143" spans="1:8">
@@ -15210,17 +15193,17 @@
       <c r="D143">
         <v>0</v>
       </c>
-      <c r="E143" s="1" t="s">
-        <v>526</v>
-      </c>
-      <c r="F143" s="2" t="s">
-        <v>511</v>
+      <c r="E143" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="F143" s="1" t="s">
+        <v>512</v>
       </c>
       <c r="G143" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H143" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="144" spans="1:8">
@@ -15243,10 +15226,10 @@
         <v>428</v>
       </c>
       <c r="G144" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H144" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="145" spans="1:9">
@@ -15265,11 +15248,11 @@
       <c r="E145" t="s">
         <v>431</v>
       </c>
-      <c r="F145" s="2" t="s">
-        <v>530</v>
-      </c>
-      <c r="H145" s="2" t="s">
+      <c r="F145" s="1" t="s">
         <v>531</v>
+      </c>
+      <c r="H145" s="1" t="s">
+        <v>532</v>
       </c>
       <c r="I145" t="s">
         <v>434</v>
@@ -15291,11 +15274,11 @@
       <c r="E146" t="s">
         <v>436</v>
       </c>
-      <c r="F146" s="2" t="s">
-        <v>530</v>
-      </c>
-      <c r="H146" s="2" t="s">
+      <c r="F146" s="1" t="s">
         <v>531</v>
+      </c>
+      <c r="H146" s="1" t="s">
+        <v>532</v>
       </c>
       <c r="I146" t="s">
         <v>434</v>
@@ -15317,11 +15300,11 @@
       <c r="E147" t="s">
         <v>438</v>
       </c>
-      <c r="F147" s="2" t="s">
-        <v>530</v>
-      </c>
-      <c r="H147" s="2" t="s">
+      <c r="F147" s="1" t="s">
         <v>531</v>
+      </c>
+      <c r="H147" s="1" t="s">
+        <v>532</v>
       </c>
       <c r="I147" t="s">
         <v>434</v>
@@ -15343,11 +15326,11 @@
       <c r="E148" t="s">
         <v>440</v>
       </c>
-      <c r="F148" s="2" t="s">
-        <v>530</v>
-      </c>
-      <c r="H148" s="2" t="s">
+      <c r="F148" s="1" t="s">
         <v>531</v>
+      </c>
+      <c r="H148" s="1" t="s">
+        <v>532</v>
       </c>
       <c r="I148" t="s">
         <v>434</v>
@@ -15369,10 +15352,8 @@
       <c r="E149" t="s">
         <v>351</v>
       </c>
-      <c r="F149"/>
-      <c r="G149"/>
       <c r="H149" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="150" spans="1:8">
@@ -15391,10 +15372,8 @@
       <c r="E150" t="s">
         <v>354</v>
       </c>
-      <c r="F150"/>
-      <c r="G150"/>
       <c r="H150" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="151" spans="1:8">
@@ -15413,10 +15392,8 @@
       <c r="E151" t="s">
         <v>356</v>
       </c>
-      <c r="F151"/>
-      <c r="G151"/>
       <c r="H151" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="152" spans="1:8">
@@ -15435,10 +15412,8 @@
       <c r="E152" t="s">
         <v>358</v>
       </c>
-      <c r="F152"/>
-      <c r="G152"/>
       <c r="H152" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
   </sheetData>

--- a/doc/cmu_soe_cfg.xlsx
+++ b/doc/cmu_soe_cfg.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2078" uniqueCount="534">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2077" uniqueCount="534">
   <si>
     <t>id</t>
   </si>
@@ -1390,6 +1390,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>门限电压</t>
     </r>
     <r>
@@ -1698,6 +1703,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>{"evt_id":{"0":"KM+","1":"KM-","2":"KMR","3":"QF"},"evt_threshold":{"AA55":"</t>
     </r>
     <r>
@@ -1877,9 +1887,9 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="0"/>
       <name val="宋体"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1891,15 +1901,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1907,6 +1917,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1921,7 +1938,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1958,6 +1975,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
@@ -1970,14 +1995,6 @@
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2005,23 +2022,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2036,19 +2046,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2072,19 +2118,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2096,13 +2130,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2114,13 +2154,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2132,55 +2184,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2192,31 +2214,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2231,6 +2241,21 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
@@ -2241,21 +2266,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2313,16 +2323,16 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
+      <right style="double">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
+      <top style="double">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
+      <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -2330,148 +2340,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -11687,21 +11697,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I152"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
+  <dimension ref="A1:H152"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="4.57142857142857" customWidth="1"/>
     <col min="2" max="2" width="4.28571428571429" customWidth="1"/>
     <col min="3" max="3" width="9.71428571428571" customWidth="1"/>
-    <col min="4" max="4" width="9.42857142857143" customWidth="1"/>
-    <col min="5" max="5" width="27" customWidth="1"/>
-    <col min="6" max="6" width="41.1428571428571" customWidth="1"/>
-    <col min="7" max="7" width="31.7142857142857" customWidth="1"/>
-    <col min="8" max="8" width="30.4285714285714" customWidth="1"/>
-    <col min="9" max="9" width="101" customWidth="1"/>
+    <col min="4" max="4" width="27" customWidth="1"/>
+    <col min="5" max="5" width="41.1428571428571" customWidth="1"/>
+    <col min="6" max="6" width="31.7142857142857" customWidth="1"/>
+    <col min="7" max="7" width="30.4285714285714" customWidth="1"/>
+    <col min="8" max="8" width="101" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -11712,25 +11721,22 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H1" t="s">
-        <v>9</v>
-      </c>
-      <c r="I1" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>1</v>
       </c>
@@ -11740,49 +11746,43 @@
       <c r="C2">
         <v>1</v>
       </c>
-      <c r="D2">
-        <v>0</v>
+      <c r="D2" t="s">
+        <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F2" t="s">
+        <v>443</v>
+      </c>
+      <c r="G2" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" t="s">
         <v>19</v>
       </c>
-      <c r="G2" t="s">
+      <c r="F3" t="s">
         <v>443</v>
       </c>
-      <c r="H2" t="s">
+      <c r="G3" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" t="s">
-        <v>443</v>
-      </c>
-      <c r="H3" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:7">
       <c r="A4">
         <v>3</v>
       </c>
@@ -11792,23 +11792,20 @@
       <c r="C4">
         <v>3</v>
       </c>
-      <c r="D4">
-        <v>0</v>
+      <c r="D4" t="s">
+        <v>30</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F4" t="s">
-        <v>31</v>
+        <v>445</v>
       </c>
       <c r="G4" t="s">
-        <v>445</v>
-      </c>
-      <c r="H4" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>4</v>
       </c>
@@ -11818,23 +11815,20 @@
       <c r="C5">
         <v>4</v>
       </c>
-      <c r="D5">
-        <v>0</v>
+      <c r="D5" t="s">
+        <v>36</v>
       </c>
       <c r="E5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F5" t="s">
-        <v>31</v>
+        <v>445</v>
       </c>
       <c r="G5" t="s">
-        <v>445</v>
-      </c>
-      <c r="H5" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>5</v>
       </c>
@@ -11844,23 +11838,20 @@
       <c r="C6">
         <v>5</v>
       </c>
-      <c r="D6">
-        <v>0</v>
+      <c r="D6" t="s">
+        <v>40</v>
       </c>
       <c r="E6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F6" t="s">
-        <v>41</v>
-      </c>
-      <c r="G6" t="s">
         <v>446</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="G6" s="1" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>6</v>
       </c>
@@ -11870,23 +11861,20 @@
       <c r="C7">
         <v>6</v>
       </c>
-      <c r="D7">
-        <v>0</v>
+      <c r="D7" t="s">
+        <v>45</v>
       </c>
       <c r="E7" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F7" t="s">
-        <v>41</v>
+        <v>446</v>
       </c>
       <c r="G7" t="s">
-        <v>446</v>
-      </c>
-      <c r="H7" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>7</v>
       </c>
@@ -11896,23 +11884,20 @@
       <c r="C8">
         <v>7</v>
       </c>
-      <c r="D8">
-        <v>0</v>
+      <c r="D8" t="s">
+        <v>49</v>
       </c>
       <c r="E8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F8" t="s">
-        <v>50</v>
+        <v>448</v>
       </c>
       <c r="G8" t="s">
-        <v>448</v>
-      </c>
-      <c r="H8" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>8</v>
       </c>
@@ -11922,23 +11907,20 @@
       <c r="C9">
         <v>8</v>
       </c>
-      <c r="D9">
-        <v>0</v>
+      <c r="D9" t="s">
+        <v>55</v>
       </c>
       <c r="E9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F9" t="s">
-        <v>56</v>
+        <v>448</v>
       </c>
       <c r="G9" t="s">
-        <v>448</v>
-      </c>
-      <c r="H9" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>9</v>
       </c>
@@ -11948,23 +11930,20 @@
       <c r="C10">
         <v>9</v>
       </c>
-      <c r="D10">
-        <v>0</v>
+      <c r="D10" t="s">
+        <v>59</v>
       </c>
       <c r="E10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F10" t="s">
-        <v>60</v>
+        <v>450</v>
       </c>
       <c r="G10" t="s">
-        <v>450</v>
-      </c>
-      <c r="H10" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:7">
       <c r="A11">
         <v>10</v>
       </c>
@@ -11974,23 +11953,20 @@
       <c r="C11">
         <v>10</v>
       </c>
-      <c r="D11">
-        <v>0</v>
+      <c r="D11" t="s">
+        <v>65</v>
       </c>
       <c r="E11" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="F11" t="s">
-        <v>60</v>
+        <v>450</v>
       </c>
       <c r="G11" t="s">
-        <v>450</v>
-      </c>
-      <c r="H11" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:7">
       <c r="A12">
         <v>11</v>
       </c>
@@ -12000,23 +11976,20 @@
       <c r="C12">
         <v>11</v>
       </c>
-      <c r="D12">
-        <v>0</v>
+      <c r="D12" t="s">
+        <v>68</v>
       </c>
       <c r="E12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F12" t="s">
-        <v>69</v>
+        <v>452</v>
       </c>
       <c r="G12" t="s">
-        <v>452</v>
-      </c>
-      <c r="H12" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:7">
       <c r="A13">
         <v>12</v>
       </c>
@@ -12026,23 +11999,20 @@
       <c r="C13">
         <v>12</v>
       </c>
-      <c r="D13">
-        <v>0</v>
+      <c r="D13" t="s">
+        <v>73</v>
       </c>
       <c r="E13" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F13" t="s">
-        <v>69</v>
+        <v>452</v>
       </c>
       <c r="G13" t="s">
-        <v>452</v>
-      </c>
-      <c r="H13" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:7">
       <c r="A14">
         <v>13</v>
       </c>
@@ -12052,23 +12022,20 @@
       <c r="C14">
         <v>13</v>
       </c>
-      <c r="D14">
-        <v>0</v>
+      <c r="D14" t="s">
+        <v>76</v>
       </c>
       <c r="E14" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F14" t="s">
-        <v>77</v>
+        <v>454</v>
       </c>
       <c r="G14" t="s">
-        <v>454</v>
-      </c>
-      <c r="H14" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:7">
       <c r="A15">
         <v>14</v>
       </c>
@@ -12078,23 +12045,20 @@
       <c r="C15">
         <v>14</v>
       </c>
-      <c r="D15">
-        <v>0</v>
+      <c r="D15" t="s">
+        <v>81</v>
       </c>
       <c r="E15" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="F15" t="s">
-        <v>77</v>
+        <v>454</v>
       </c>
       <c r="G15" t="s">
-        <v>454</v>
-      </c>
-      <c r="H15" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:7">
       <c r="A16">
         <v>15</v>
       </c>
@@ -12104,23 +12068,20 @@
       <c r="C16">
         <v>15</v>
       </c>
-      <c r="D16">
-        <v>0</v>
+      <c r="D16" t="s">
+        <v>84</v>
       </c>
       <c r="E16" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F16" t="s">
-        <v>85</v>
+        <v>455</v>
       </c>
       <c r="G16" t="s">
-        <v>455</v>
-      </c>
-      <c r="H16" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:7">
       <c r="A17">
         <v>16</v>
       </c>
@@ -12130,23 +12091,20 @@
       <c r="C17">
         <v>16</v>
       </c>
-      <c r="D17">
-        <v>0</v>
+      <c r="D17" t="s">
+        <v>89</v>
       </c>
       <c r="E17" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="F17" t="s">
-        <v>85</v>
+        <v>455</v>
       </c>
       <c r="G17" t="s">
-        <v>455</v>
-      </c>
-      <c r="H17" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:7">
       <c r="A18">
         <v>17</v>
       </c>
@@ -12156,23 +12114,20 @@
       <c r="C18">
         <v>17</v>
       </c>
-      <c r="D18">
-        <v>0</v>
+      <c r="D18" t="s">
+        <v>92</v>
       </c>
       <c r="E18" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F18" t="s">
-        <v>93</v>
+        <v>456</v>
       </c>
       <c r="G18" t="s">
-        <v>456</v>
-      </c>
-      <c r="H18" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:7">
       <c r="A19">
         <v>18</v>
       </c>
@@ -12182,23 +12137,20 @@
       <c r="C19">
         <v>18</v>
       </c>
-      <c r="D19">
-        <v>0</v>
+      <c r="D19" t="s">
+        <v>97</v>
       </c>
       <c r="E19" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F19" t="s">
-        <v>98</v>
+        <v>456</v>
       </c>
       <c r="G19" t="s">
-        <v>456</v>
-      </c>
-      <c r="H19" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:7">
       <c r="A20">
         <v>19</v>
       </c>
@@ -12208,23 +12160,20 @@
       <c r="C20">
         <v>19</v>
       </c>
-      <c r="D20">
-        <v>0</v>
+      <c r="D20" t="s">
+        <v>102</v>
       </c>
       <c r="E20" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F20" t="s">
-        <v>103</v>
+        <v>457</v>
       </c>
       <c r="G20" t="s">
-        <v>457</v>
-      </c>
-      <c r="H20" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:7">
       <c r="A21">
         <v>20</v>
       </c>
@@ -12234,23 +12183,20 @@
       <c r="C21">
         <v>20</v>
       </c>
-      <c r="D21">
-        <v>0</v>
+      <c r="D21" t="s">
+        <v>107</v>
       </c>
       <c r="E21" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="F21" t="s">
-        <v>103</v>
+        <v>457</v>
       </c>
       <c r="G21" t="s">
-        <v>457</v>
-      </c>
-      <c r="H21" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:7">
       <c r="A22">
         <v>21</v>
       </c>
@@ -12260,23 +12206,20 @@
       <c r="C22">
         <v>21</v>
       </c>
-      <c r="D22">
-        <v>0</v>
+      <c r="D22" t="s">
+        <v>110</v>
       </c>
       <c r="E22" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F22" t="s">
-        <v>111</v>
+        <v>458</v>
       </c>
       <c r="G22" t="s">
-        <v>458</v>
-      </c>
-      <c r="H22" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:7">
       <c r="A23">
         <v>22</v>
       </c>
@@ -12286,20 +12229,17 @@
       <c r="C23">
         <v>22</v>
       </c>
-      <c r="D23">
-        <v>0</v>
-      </c>
-      <c r="E23" t="s">
+      <c r="D23" t="s">
         <v>115</v>
       </c>
+      <c r="F23" t="s">
+        <v>459</v>
+      </c>
       <c r="G23" t="s">
-        <v>459</v>
-      </c>
-      <c r="H23" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" spans="1:7">
       <c r="A24">
         <v>23</v>
       </c>
@@ -12309,20 +12249,17 @@
       <c r="C24">
         <v>23</v>
       </c>
-      <c r="D24">
-        <v>0</v>
-      </c>
-      <c r="E24" t="s">
+      <c r="D24" t="s">
         <v>121</v>
       </c>
+      <c r="F24" t="s">
+        <v>459</v>
+      </c>
       <c r="G24" t="s">
-        <v>459</v>
-      </c>
-      <c r="H24" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" spans="1:7">
       <c r="A25">
         <v>24</v>
       </c>
@@ -12332,20 +12269,17 @@
       <c r="C25">
         <v>24</v>
       </c>
-      <c r="D25">
-        <v>0</v>
-      </c>
-      <c r="E25" t="s">
+      <c r="D25" t="s">
         <v>125</v>
       </c>
+      <c r="F25" t="s">
+        <v>459</v>
+      </c>
       <c r="G25" t="s">
-        <v>459</v>
-      </c>
-      <c r="H25" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" spans="1:7">
       <c r="A26">
         <v>25</v>
       </c>
@@ -12355,20 +12289,17 @@
       <c r="C26">
         <v>25</v>
       </c>
-      <c r="D26">
-        <v>0</v>
-      </c>
-      <c r="E26" t="s">
+      <c r="D26" t="s">
         <v>129</v>
       </c>
+      <c r="F26" t="s">
+        <v>459</v>
+      </c>
       <c r="G26" t="s">
-        <v>459</v>
-      </c>
-      <c r="H26" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" spans="1:7">
       <c r="A27">
         <v>26</v>
       </c>
@@ -12378,20 +12309,17 @@
       <c r="C27">
         <v>26</v>
       </c>
-      <c r="D27">
-        <v>0</v>
-      </c>
-      <c r="E27" t="s">
+      <c r="D27" t="s">
         <v>133</v>
       </c>
+      <c r="F27" t="s">
+        <v>461</v>
+      </c>
       <c r="G27" t="s">
-        <v>461</v>
-      </c>
-      <c r="H27" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="28" spans="1:8">
+    <row r="28" spans="1:7">
       <c r="A28">
         <v>27</v>
       </c>
@@ -12401,20 +12329,17 @@
       <c r="C28">
         <v>27</v>
       </c>
-      <c r="D28">
-        <v>0</v>
-      </c>
-      <c r="E28" t="s">
+      <c r="D28" t="s">
         <v>138</v>
       </c>
+      <c r="F28" t="s">
+        <v>461</v>
+      </c>
       <c r="G28" t="s">
-        <v>461</v>
-      </c>
-      <c r="H28" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" spans="1:7">
       <c r="A29">
         <v>28</v>
       </c>
@@ -12424,20 +12349,17 @@
       <c r="C29">
         <v>28</v>
       </c>
-      <c r="D29">
-        <v>0</v>
-      </c>
-      <c r="E29" t="s">
+      <c r="D29" t="s">
         <v>141</v>
       </c>
+      <c r="F29" t="s">
+        <v>461</v>
+      </c>
       <c r="G29" t="s">
-        <v>461</v>
-      </c>
-      <c r="H29" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" spans="1:7">
       <c r="A30">
         <v>29</v>
       </c>
@@ -12447,20 +12369,17 @@
       <c r="C30">
         <v>29</v>
       </c>
-      <c r="D30">
-        <v>0</v>
-      </c>
-      <c r="E30" t="s">
+      <c r="D30" t="s">
         <v>144</v>
       </c>
+      <c r="F30" t="s">
+        <v>461</v>
+      </c>
       <c r="G30" t="s">
-        <v>461</v>
-      </c>
-      <c r="H30" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" spans="1:7">
       <c r="A31">
         <v>30</v>
       </c>
@@ -12470,20 +12389,17 @@
       <c r="C31">
         <v>30</v>
       </c>
-      <c r="D31">
-        <v>0</v>
-      </c>
-      <c r="E31" t="s">
+      <c r="D31" t="s">
         <v>148</v>
       </c>
+      <c r="F31" t="s">
+        <v>461</v>
+      </c>
       <c r="G31" t="s">
-        <v>461</v>
-      </c>
-      <c r="H31" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32" spans="1:7">
       <c r="A32">
         <v>31</v>
       </c>
@@ -12493,20 +12409,17 @@
       <c r="C32">
         <v>31</v>
       </c>
-      <c r="D32">
-        <v>0</v>
-      </c>
-      <c r="E32" t="s">
+      <c r="D32" t="s">
         <v>151</v>
       </c>
+      <c r="F32" t="s">
+        <v>463</v>
+      </c>
       <c r="G32" t="s">
-        <v>463</v>
-      </c>
-      <c r="H32" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="33" spans="1:8">
+    <row r="33" spans="1:7">
       <c r="A33">
         <v>32</v>
       </c>
@@ -12516,20 +12429,17 @@
       <c r="C33">
         <v>32</v>
       </c>
-      <c r="D33">
-        <v>0</v>
-      </c>
-      <c r="E33" t="s">
+      <c r="D33" t="s">
         <v>156</v>
       </c>
+      <c r="F33" t="s">
+        <v>463</v>
+      </c>
       <c r="G33" t="s">
-        <v>463</v>
-      </c>
-      <c r="H33" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="34" spans="1:8">
+    <row r="34" spans="1:7">
       <c r="A34">
         <v>33</v>
       </c>
@@ -12539,20 +12449,17 @@
       <c r="C34">
         <v>33</v>
       </c>
-      <c r="D34">
-        <v>0</v>
-      </c>
-      <c r="E34" t="s">
+      <c r="D34" t="s">
         <v>159</v>
       </c>
+      <c r="F34" t="s">
+        <v>465</v>
+      </c>
       <c r="G34" t="s">
-        <v>465</v>
-      </c>
-      <c r="H34" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="35" spans="1:8">
+    <row r="35" spans="1:7">
       <c r="A35">
         <v>34</v>
       </c>
@@ -12562,20 +12469,17 @@
       <c r="C35">
         <v>34</v>
       </c>
-      <c r="D35">
-        <v>0</v>
-      </c>
-      <c r="E35" t="s">
+      <c r="D35" t="s">
         <v>163</v>
       </c>
+      <c r="F35" t="s">
+        <v>465</v>
+      </c>
       <c r="G35" t="s">
-        <v>465</v>
-      </c>
-      <c r="H35" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="36" spans="1:8">
+    <row r="36" spans="1:7">
       <c r="A36">
         <v>35</v>
       </c>
@@ -12585,23 +12489,20 @@
       <c r="C36">
         <v>35</v>
       </c>
-      <c r="D36">
-        <v>0</v>
+      <c r="D36" t="s">
+        <v>166</v>
       </c>
       <c r="E36" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F36" t="s">
-        <v>167</v>
+        <v>459</v>
       </c>
       <c r="G36" t="s">
-        <v>459</v>
-      </c>
-      <c r="H36" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="37" spans="1:8">
+    <row r="37" spans="1:7">
       <c r="A37">
         <v>36</v>
       </c>
@@ -12611,23 +12512,20 @@
       <c r="C37">
         <v>36</v>
       </c>
-      <c r="D37">
-        <v>0</v>
+      <c r="D37" t="s">
+        <v>170</v>
       </c>
       <c r="E37" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F37" t="s">
-        <v>167</v>
+        <v>467</v>
       </c>
       <c r="G37" t="s">
-        <v>467</v>
-      </c>
-      <c r="H37" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="38" spans="1:8">
+    <row r="38" spans="1:7">
       <c r="A38">
         <v>37</v>
       </c>
@@ -12637,23 +12535,20 @@
       <c r="C38">
         <v>37</v>
       </c>
-      <c r="D38">
-        <v>0</v>
+      <c r="D38" t="s">
+        <v>174</v>
       </c>
       <c r="E38" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="F38" t="s">
-        <v>167</v>
+        <v>459</v>
       </c>
       <c r="G38" t="s">
-        <v>459</v>
-      </c>
-      <c r="H38" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="39" spans="1:8">
+    <row r="39" spans="1:7">
       <c r="A39">
         <v>38</v>
       </c>
@@ -12663,23 +12558,20 @@
       <c r="C39">
         <v>38</v>
       </c>
-      <c r="D39">
-        <v>0</v>
+      <c r="D39" t="s">
+        <v>177</v>
       </c>
       <c r="E39" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="F39" t="s">
-        <v>167</v>
+        <v>467</v>
       </c>
       <c r="G39" t="s">
-        <v>467</v>
-      </c>
-      <c r="H39" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="40" spans="1:8">
+    <row r="40" spans="1:7">
       <c r="A40">
         <v>39</v>
       </c>
@@ -12689,23 +12581,20 @@
       <c r="C40">
         <v>39</v>
       </c>
-      <c r="D40">
-        <v>0</v>
+      <c r="D40" t="s">
+        <v>180</v>
       </c>
       <c r="E40" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="F40" t="s">
-        <v>167</v>
+        <v>467</v>
       </c>
       <c r="G40" t="s">
-        <v>467</v>
-      </c>
-      <c r="H40" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="41" spans="1:8">
+    <row r="41" spans="1:7">
       <c r="A41">
         <v>40</v>
       </c>
@@ -12715,23 +12604,20 @@
       <c r="C41">
         <v>40</v>
       </c>
-      <c r="D41">
-        <v>0</v>
+      <c r="D41" t="s">
+        <v>183</v>
       </c>
       <c r="E41" t="s">
-        <v>183</v>
+        <v>167</v>
       </c>
       <c r="F41" t="s">
-        <v>167</v>
+        <v>467</v>
       </c>
       <c r="G41" t="s">
-        <v>467</v>
-      </c>
-      <c r="H41" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="42" spans="1:8">
+    <row r="42" spans="1:7">
       <c r="A42">
         <v>41</v>
       </c>
@@ -12741,23 +12627,20 @@
       <c r="C42">
         <v>41</v>
       </c>
-      <c r="D42">
-        <v>0</v>
+      <c r="D42" t="s">
+        <v>186</v>
       </c>
       <c r="E42" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F42" t="s">
-        <v>187</v>
+        <v>469</v>
       </c>
       <c r="G42" t="s">
-        <v>469</v>
-      </c>
-      <c r="H42" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="43" spans="1:8">
+    <row r="43" spans="1:7">
       <c r="A43">
         <v>42</v>
       </c>
@@ -12767,23 +12650,20 @@
       <c r="C43">
         <v>42</v>
       </c>
-      <c r="D43">
-        <v>0</v>
+      <c r="D43" t="s">
+        <v>191</v>
       </c>
       <c r="E43" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="F43" t="s">
-        <v>187</v>
+        <v>469</v>
       </c>
       <c r="G43" t="s">
-        <v>469</v>
-      </c>
-      <c r="H43" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="44" spans="1:8">
+    <row r="44" spans="1:7">
       <c r="A44">
         <v>43</v>
       </c>
@@ -12793,20 +12673,17 @@
       <c r="C44">
         <v>43</v>
       </c>
-      <c r="D44">
-        <v>0</v>
-      </c>
-      <c r="E44" t="s">
+      <c r="D44" t="s">
         <v>194</v>
       </c>
+      <c r="F44" t="s">
+        <v>470</v>
+      </c>
       <c r="G44" t="s">
-        <v>470</v>
-      </c>
-      <c r="H44" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="45" spans="1:8">
+    <row r="45" spans="1:7">
       <c r="A45">
         <v>44</v>
       </c>
@@ -12816,20 +12693,17 @@
       <c r="C45">
         <v>44</v>
       </c>
-      <c r="D45">
-        <v>0</v>
-      </c>
-      <c r="E45" t="s">
+      <c r="D45" t="s">
         <v>198</v>
       </c>
+      <c r="F45" t="s">
+        <v>471</v>
+      </c>
       <c r="G45" t="s">
-        <v>471</v>
-      </c>
-      <c r="H45" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="46" spans="1:8">
+    <row r="46" spans="1:7">
       <c r="A46">
         <v>45</v>
       </c>
@@ -12839,20 +12713,17 @@
       <c r="C46">
         <v>45</v>
       </c>
-      <c r="D46">
-        <v>0</v>
-      </c>
-      <c r="E46" t="s">
+      <c r="D46" t="s">
         <v>202</v>
       </c>
+      <c r="F46" t="s">
+        <v>472</v>
+      </c>
       <c r="G46" t="s">
-        <v>472</v>
-      </c>
-      <c r="H46" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="47" spans="1:8">
+    <row r="47" spans="1:7">
       <c r="A47">
         <v>46</v>
       </c>
@@ -12862,20 +12733,17 @@
       <c r="C47">
         <v>46</v>
       </c>
-      <c r="D47">
-        <v>0</v>
-      </c>
-      <c r="E47" t="s">
+      <c r="D47" t="s">
         <v>206</v>
       </c>
+      <c r="F47" t="s">
+        <v>471</v>
+      </c>
       <c r="G47" t="s">
-        <v>471</v>
-      </c>
-      <c r="H47" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="48" spans="1:8">
+    <row r="48" spans="1:7">
       <c r="A48">
         <v>47</v>
       </c>
@@ -12885,20 +12753,17 @@
       <c r="C48">
         <v>47</v>
       </c>
-      <c r="D48">
-        <v>0</v>
-      </c>
-      <c r="E48" t="s">
+      <c r="D48" t="s">
         <v>209</v>
       </c>
+      <c r="F48" t="s">
+        <v>472</v>
+      </c>
       <c r="G48" t="s">
-        <v>472</v>
-      </c>
-      <c r="H48" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="49" spans="1:8">
+    <row r="49" spans="1:7">
       <c r="A49">
         <v>48</v>
       </c>
@@ -12908,20 +12773,17 @@
       <c r="C49">
         <v>48</v>
       </c>
-      <c r="D49">
-        <v>0</v>
-      </c>
-      <c r="E49" t="s">
+      <c r="D49" t="s">
         <v>212</v>
       </c>
+      <c r="F49" t="s">
+        <v>473</v>
+      </c>
       <c r="G49" t="s">
-        <v>473</v>
-      </c>
-      <c r="H49" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="50" spans="1:8">
+    <row r="50" spans="1:7">
       <c r="A50">
         <v>49</v>
       </c>
@@ -12931,20 +12793,17 @@
       <c r="C50">
         <v>49</v>
       </c>
-      <c r="D50">
-        <v>0</v>
-      </c>
-      <c r="E50" t="s">
+      <c r="D50" t="s">
         <v>216</v>
       </c>
+      <c r="F50" t="s">
+        <v>473</v>
+      </c>
       <c r="G50" t="s">
-        <v>473</v>
-      </c>
-      <c r="H50" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="51" spans="1:8">
+    <row r="51" spans="1:7">
       <c r="A51">
         <v>50</v>
       </c>
@@ -12954,20 +12813,17 @@
       <c r="C51">
         <v>50</v>
       </c>
-      <c r="D51">
-        <v>0</v>
-      </c>
-      <c r="E51" t="s">
+      <c r="D51" t="s">
         <v>219</v>
+      </c>
+      <c r="F51" t="s">
+        <v>468</v>
       </c>
       <c r="G51" t="s">
         <v>468</v>
       </c>
-      <c r="H51" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8">
+    </row>
+    <row r="52" spans="1:7">
       <c r="A52">
         <v>51</v>
       </c>
@@ -12977,23 +12833,20 @@
       <c r="C52">
         <v>51</v>
       </c>
-      <c r="D52">
-        <v>0</v>
+      <c r="D52" t="s">
+        <v>222</v>
       </c>
       <c r="E52" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F52" t="s">
-        <v>223</v>
+        <v>474</v>
       </c>
       <c r="G52" t="s">
-        <v>474</v>
-      </c>
-      <c r="H52" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="53" spans="1:8">
+    <row r="53" spans="1:7">
       <c r="A53">
         <v>52</v>
       </c>
@@ -13003,20 +12856,17 @@
       <c r="C53">
         <v>52</v>
       </c>
-      <c r="D53">
-        <v>0</v>
-      </c>
-      <c r="E53" s="2" t="s">
+      <c r="D53" s="2" t="s">
         <v>475</v>
+      </c>
+      <c r="F53" t="s">
+        <v>468</v>
       </c>
       <c r="G53" t="s">
         <v>468</v>
       </c>
-      <c r="H53" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8">
+    </row>
+    <row r="54" spans="1:7">
       <c r="A54">
         <v>53</v>
       </c>
@@ -13026,20 +12876,17 @@
       <c r="C54">
         <v>53</v>
       </c>
-      <c r="D54">
-        <v>0</v>
-      </c>
-      <c r="E54" t="s">
+      <c r="D54" t="s">
         <v>230</v>
       </c>
-      <c r="G54" s="2" t="s">
+      <c r="F54" s="2" t="s">
         <v>476</v>
       </c>
-      <c r="H54" t="s">
+      <c r="G54" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="55" spans="1:8">
+    <row r="55" spans="1:7">
       <c r="A55">
         <v>54</v>
       </c>
@@ -13049,20 +12896,17 @@
       <c r="C55">
         <v>54</v>
       </c>
-      <c r="D55">
-        <v>0</v>
-      </c>
-      <c r="E55" s="2" t="s">
+      <c r="D55" s="2" t="s">
         <v>477</v>
       </c>
+      <c r="F55" t="s">
+        <v>478</v>
+      </c>
       <c r="G55" t="s">
-        <v>478</v>
-      </c>
-      <c r="H55" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="56" spans="1:8">
+    <row r="56" spans="1:7">
       <c r="A56">
         <v>55</v>
       </c>
@@ -13072,20 +12916,17 @@
       <c r="C56">
         <v>55</v>
       </c>
-      <c r="D56">
-        <v>0</v>
-      </c>
-      <c r="E56" t="s">
+      <c r="D56" t="s">
         <v>238</v>
+      </c>
+      <c r="F56" t="s">
+        <v>468</v>
       </c>
       <c r="G56" t="s">
         <v>468</v>
       </c>
-      <c r="H56" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8">
+    </row>
+    <row r="57" spans="1:7">
       <c r="A57">
         <v>56</v>
       </c>
@@ -13095,20 +12936,17 @@
       <c r="C57">
         <v>56</v>
       </c>
-      <c r="D57">
-        <v>0</v>
-      </c>
-      <c r="E57" t="s">
+      <c r="D57" t="s">
         <v>241</v>
       </c>
+      <c r="F57" t="s">
+        <v>479</v>
+      </c>
       <c r="G57" t="s">
-        <v>479</v>
-      </c>
-      <c r="H57" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="58" spans="1:8">
+    <row r="58" spans="1:7">
       <c r="A58">
         <v>57</v>
       </c>
@@ -13118,20 +12956,17 @@
       <c r="C58">
         <v>57</v>
       </c>
-      <c r="D58">
-        <v>0</v>
-      </c>
-      <c r="E58" t="s">
+      <c r="D58" t="s">
         <v>245</v>
       </c>
+      <c r="F58" t="s">
+        <v>478</v>
+      </c>
       <c r="G58" t="s">
-        <v>478</v>
-      </c>
-      <c r="H58" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="59" spans="1:8">
+    <row r="59" spans="1:7">
       <c r="A59">
         <v>58</v>
       </c>
@@ -13141,23 +12976,20 @@
       <c r="C59">
         <v>58</v>
       </c>
-      <c r="D59">
-        <v>0</v>
+      <c r="D59" t="s">
+        <v>248</v>
       </c>
       <c r="E59" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F59" t="s">
-        <v>249</v>
+        <v>468</v>
       </c>
       <c r="G59" t="s">
         <v>468</v>
       </c>
-      <c r="H59" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8">
+    </row>
+    <row r="60" spans="1:7">
       <c r="A60">
         <v>59</v>
       </c>
@@ -13167,20 +12999,17 @@
       <c r="C60">
         <v>59</v>
       </c>
-      <c r="D60">
-        <v>0</v>
-      </c>
-      <c r="E60" t="s">
+      <c r="D60" t="s">
         <v>252</v>
+      </c>
+      <c r="F60" t="s">
+        <v>468</v>
       </c>
       <c r="G60" t="s">
         <v>468</v>
       </c>
-      <c r="H60" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8">
+    </row>
+    <row r="61" spans="1:7">
       <c r="A61">
         <v>60</v>
       </c>
@@ -13190,20 +13019,17 @@
       <c r="C61">
         <v>60</v>
       </c>
-      <c r="D61">
-        <v>0</v>
-      </c>
-      <c r="E61" t="s">
+      <c r="D61" t="s">
         <v>480</v>
+      </c>
+      <c r="F61" t="s">
+        <v>468</v>
       </c>
       <c r="G61" t="s">
         <v>468</v>
       </c>
-      <c r="H61" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8">
+    </row>
+    <row r="62" spans="1:7">
       <c r="A62">
         <v>61</v>
       </c>
@@ -13213,20 +13039,17 @@
       <c r="C62">
         <v>61</v>
       </c>
-      <c r="D62">
-        <v>0</v>
-      </c>
-      <c r="E62" t="s">
+      <c r="D62" t="s">
         <v>331</v>
+      </c>
+      <c r="F62" t="s">
+        <v>468</v>
       </c>
       <c r="G62" t="s">
         <v>468</v>
       </c>
-      <c r="H62" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8">
+    </row>
+    <row r="63" spans="1:7">
       <c r="A63">
         <v>62</v>
       </c>
@@ -13236,20 +13059,17 @@
       <c r="C63">
         <v>62</v>
       </c>
-      <c r="D63">
-        <v>0</v>
-      </c>
-      <c r="E63" t="s">
+      <c r="D63" t="s">
         <v>333</v>
+      </c>
+      <c r="F63" t="s">
+        <v>468</v>
       </c>
       <c r="G63" t="s">
         <v>468</v>
       </c>
-      <c r="H63" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8">
+    </row>
+    <row r="64" spans="1:7">
       <c r="A64">
         <v>63</v>
       </c>
@@ -13259,20 +13079,17 @@
       <c r="C64">
         <v>63</v>
       </c>
-      <c r="D64">
-        <v>0</v>
-      </c>
-      <c r="E64" t="s">
+      <c r="D64" t="s">
         <v>335</v>
       </c>
+      <c r="F64" t="s">
+        <v>481</v>
+      </c>
       <c r="G64" t="s">
-        <v>481</v>
-      </c>
-      <c r="H64" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="65" spans="1:8">
+    <row r="65" spans="1:7">
       <c r="A65">
         <v>64</v>
       </c>
@@ -13282,20 +13099,17 @@
       <c r="C65">
         <v>64</v>
       </c>
-      <c r="D65">
-        <v>0</v>
-      </c>
-      <c r="E65" t="s">
+      <c r="D65" t="s">
         <v>337</v>
       </c>
+      <c r="F65" t="s">
+        <v>481</v>
+      </c>
       <c r="G65" t="s">
-        <v>481</v>
-      </c>
-      <c r="H65" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="66" spans="1:8">
+    <row r="66" spans="1:7">
       <c r="A66">
         <v>65</v>
       </c>
@@ -13305,20 +13119,17 @@
       <c r="C66">
         <v>65</v>
       </c>
-      <c r="D66">
-        <v>0</v>
-      </c>
-      <c r="E66" t="s">
+      <c r="D66" t="s">
         <v>339</v>
       </c>
+      <c r="F66" t="s">
+        <v>483</v>
+      </c>
       <c r="G66" t="s">
-        <v>483</v>
-      </c>
-      <c r="H66" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="67" spans="1:8">
+    <row r="67" spans="1:7">
       <c r="A67">
         <v>66</v>
       </c>
@@ -13328,20 +13139,17 @@
       <c r="C67">
         <v>66</v>
       </c>
-      <c r="D67">
-        <v>0</v>
-      </c>
-      <c r="E67" t="s">
+      <c r="D67" t="s">
         <v>484</v>
       </c>
+      <c r="F67" t="s">
+        <v>485</v>
+      </c>
       <c r="G67" t="s">
-        <v>485</v>
-      </c>
-      <c r="H67" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="68" spans="1:8">
+    <row r="68" spans="1:7">
       <c r="A68">
         <v>67</v>
       </c>
@@ -13351,20 +13159,17 @@
       <c r="C68">
         <v>67</v>
       </c>
-      <c r="D68">
-        <v>0</v>
-      </c>
-      <c r="E68" t="s">
+      <c r="D68" t="s">
         <v>486</v>
       </c>
+      <c r="F68" t="s">
+        <v>487</v>
+      </c>
       <c r="G68" t="s">
-        <v>487</v>
-      </c>
-      <c r="H68" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="69" spans="1:8">
+    <row r="69" spans="1:7">
       <c r="A69">
         <v>68</v>
       </c>
@@ -13374,20 +13179,17 @@
       <c r="C69">
         <v>68</v>
       </c>
-      <c r="D69">
-        <v>0</v>
-      </c>
-      <c r="E69" t="s">
+      <c r="D69" t="s">
         <v>488</v>
       </c>
+      <c r="F69" t="s">
+        <v>489</v>
+      </c>
       <c r="G69" t="s">
-        <v>489</v>
-      </c>
-      <c r="H69" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="70" spans="1:8">
+    <row r="70" spans="1:7">
       <c r="A70">
         <v>69</v>
       </c>
@@ -13397,23 +13199,20 @@
       <c r="C70">
         <v>69</v>
       </c>
-      <c r="D70">
-        <v>0</v>
+      <c r="D70" t="s">
+        <v>348</v>
       </c>
       <c r="E70" t="s">
-        <v>348</v>
+        <v>299</v>
       </c>
       <c r="F70" t="s">
-        <v>299</v>
+        <v>490</v>
       </c>
       <c r="G70" t="s">
-        <v>490</v>
-      </c>
-      <c r="H70" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="71" spans="1:8">
+    <row r="71" spans="1:7">
       <c r="A71">
         <v>70</v>
       </c>
@@ -13423,20 +13222,17 @@
       <c r="C71">
         <v>128</v>
       </c>
-      <c r="D71">
-        <v>0</v>
-      </c>
-      <c r="E71" t="s">
+      <c r="D71" t="s">
         <v>351</v>
       </c>
+      <c r="F71" t="s">
+        <v>491</v>
+      </c>
       <c r="G71" t="s">
-        <v>491</v>
-      </c>
-      <c r="H71" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="72" spans="1:8">
+    <row r="72" spans="1:7">
       <c r="A72">
         <v>71</v>
       </c>
@@ -13446,20 +13242,17 @@
       <c r="C72">
         <v>129</v>
       </c>
-      <c r="D72">
-        <v>0</v>
-      </c>
-      <c r="E72" t="s">
+      <c r="D72" t="s">
         <v>354</v>
       </c>
+      <c r="F72" t="s">
+        <v>491</v>
+      </c>
       <c r="G72" t="s">
-        <v>491</v>
-      </c>
-      <c r="H72" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="73" spans="1:8">
+    <row r="73" spans="1:7">
       <c r="A73">
         <v>72</v>
       </c>
@@ -13469,20 +13262,17 @@
       <c r="C73">
         <v>130</v>
       </c>
-      <c r="D73">
-        <v>0</v>
-      </c>
-      <c r="E73" t="s">
+      <c r="D73" t="s">
         <v>356</v>
       </c>
+      <c r="F73" t="s">
+        <v>491</v>
+      </c>
       <c r="G73" t="s">
-        <v>491</v>
-      </c>
-      <c r="H73" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="74" spans="1:8">
+    <row r="74" spans="1:7">
       <c r="A74">
         <v>73</v>
       </c>
@@ -13492,20 +13282,17 @@
       <c r="C74">
         <v>131</v>
       </c>
-      <c r="D74">
-        <v>0</v>
-      </c>
-      <c r="E74" t="s">
+      <c r="D74" t="s">
         <v>358</v>
       </c>
+      <c r="F74" t="s">
+        <v>491</v>
+      </c>
       <c r="G74" t="s">
-        <v>491</v>
-      </c>
-      <c r="H74" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="75" spans="1:8">
+    <row r="75" spans="1:7">
       <c r="A75">
         <v>74</v>
       </c>
@@ -13515,23 +13302,20 @@
       <c r="C75">
         <v>1</v>
       </c>
-      <c r="D75">
-        <v>0</v>
+      <c r="D75" t="s">
+        <v>18</v>
       </c>
       <c r="E75" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F75" t="s">
-        <v>19</v>
+        <v>443</v>
       </c>
       <c r="G75" t="s">
-        <v>443</v>
-      </c>
-      <c r="H75" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="76" spans="1:8">
+    <row r="76" spans="1:7">
       <c r="A76">
         <v>75</v>
       </c>
@@ -13541,23 +13325,20 @@
       <c r="C76">
         <v>2</v>
       </c>
-      <c r="D76">
-        <v>0</v>
+      <c r="D76" t="s">
+        <v>26</v>
       </c>
       <c r="E76" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F76" t="s">
-        <v>19</v>
+        <v>443</v>
       </c>
       <c r="G76" t="s">
-        <v>443</v>
-      </c>
-      <c r="H76" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="77" spans="1:8">
+    <row r="77" spans="1:7">
       <c r="A77">
         <v>76</v>
       </c>
@@ -13567,23 +13348,20 @@
       <c r="C77">
         <v>3</v>
       </c>
-      <c r="D77">
-        <v>0</v>
+      <c r="D77" t="s">
+        <v>30</v>
       </c>
       <c r="E77" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F77" t="s">
-        <v>31</v>
+        <v>445</v>
       </c>
       <c r="G77" t="s">
-        <v>445</v>
-      </c>
-      <c r="H77" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="78" spans="1:8">
+    <row r="78" spans="1:7">
       <c r="A78">
         <v>77</v>
       </c>
@@ -13593,23 +13371,20 @@
       <c r="C78">
         <v>4</v>
       </c>
-      <c r="D78">
-        <v>0</v>
+      <c r="D78" t="s">
+        <v>36</v>
       </c>
       <c r="E78" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F78" t="s">
-        <v>31</v>
+        <v>445</v>
       </c>
       <c r="G78" t="s">
-        <v>445</v>
-      </c>
-      <c r="H78" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="79" spans="1:8">
+    <row r="79" spans="1:7">
       <c r="A79">
         <v>78</v>
       </c>
@@ -13619,20 +13394,17 @@
       <c r="C79">
         <v>5</v>
       </c>
-      <c r="D79">
-        <v>0</v>
-      </c>
-      <c r="E79" t="s">
+      <c r="D79" t="s">
         <v>364</v>
+      </c>
+      <c r="F79" t="s">
+        <v>449</v>
       </c>
       <c r="G79" t="s">
         <v>449</v>
       </c>
-      <c r="H79" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8">
+    </row>
+    <row r="80" spans="1:7">
       <c r="A80">
         <v>79</v>
       </c>
@@ -13642,20 +13414,17 @@
       <c r="C80">
         <v>6</v>
       </c>
-      <c r="D80">
-        <v>0</v>
-      </c>
-      <c r="E80" t="s">
+      <c r="D80" t="s">
         <v>365</v>
+      </c>
+      <c r="F80" t="s">
+        <v>449</v>
       </c>
       <c r="G80" t="s">
         <v>449</v>
       </c>
-      <c r="H80" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8">
+    </row>
+    <row r="81" spans="1:7">
       <c r="A81">
         <v>80</v>
       </c>
@@ -13665,23 +13434,20 @@
       <c r="C81">
         <v>7</v>
       </c>
-      <c r="D81">
-        <v>0</v>
+      <c r="D81" t="s">
+        <v>49</v>
       </c>
       <c r="E81" t="s">
-        <v>49</v>
+        <v>366</v>
       </c>
       <c r="F81" t="s">
-        <v>366</v>
+        <v>468</v>
       </c>
       <c r="G81" t="s">
-        <v>468</v>
-      </c>
-      <c r="H81" t="s">
         <v>492</v>
       </c>
     </row>
-    <row r="82" spans="1:8">
+    <row r="82" spans="1:7">
       <c r="A82">
         <v>81</v>
       </c>
@@ -13691,20 +13457,17 @@
       <c r="C82">
         <v>8</v>
       </c>
-      <c r="D82">
-        <v>0</v>
-      </c>
-      <c r="E82" t="s">
+      <c r="D82" t="s">
         <v>55</v>
       </c>
+      <c r="F82" t="s">
+        <v>493</v>
+      </c>
       <c r="G82" t="s">
-        <v>493</v>
-      </c>
-      <c r="H82" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="83" spans="1:8">
+    <row r="83" spans="1:7">
       <c r="A83">
         <v>82</v>
       </c>
@@ -13714,23 +13477,20 @@
       <c r="C83">
         <v>9</v>
       </c>
-      <c r="D83">
-        <v>0</v>
+      <c r="D83" t="s">
+        <v>59</v>
       </c>
       <c r="E83" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F83" t="s">
-        <v>60</v>
+        <v>450</v>
       </c>
       <c r="G83" t="s">
-        <v>450</v>
-      </c>
-      <c r="H83" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="84" spans="1:8">
+    <row r="84" spans="1:7">
       <c r="A84">
         <v>83</v>
       </c>
@@ -13740,23 +13500,20 @@
       <c r="C84">
         <v>10</v>
       </c>
-      <c r="D84">
-        <v>0</v>
+      <c r="D84" t="s">
+        <v>65</v>
       </c>
       <c r="E84" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="F84" t="s">
-        <v>60</v>
+        <v>450</v>
       </c>
       <c r="G84" t="s">
-        <v>450</v>
-      </c>
-      <c r="H84" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="85" spans="1:8">
+    <row r="85" spans="1:7">
       <c r="A85">
         <v>84</v>
       </c>
@@ -13766,23 +13523,20 @@
       <c r="C85">
         <v>11</v>
       </c>
-      <c r="D85">
-        <v>0</v>
+      <c r="D85" t="s">
+        <v>68</v>
       </c>
       <c r="E85" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F85" t="s">
-        <v>69</v>
+        <v>452</v>
       </c>
       <c r="G85" t="s">
-        <v>452</v>
-      </c>
-      <c r="H85" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="86" spans="1:8">
+    <row r="86" spans="1:7">
       <c r="A86">
         <v>85</v>
       </c>
@@ -13792,23 +13546,20 @@
       <c r="C86">
         <v>12</v>
       </c>
-      <c r="D86">
-        <v>0</v>
+      <c r="D86" t="s">
+        <v>73</v>
       </c>
       <c r="E86" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F86" t="s">
-        <v>69</v>
+        <v>452</v>
       </c>
       <c r="G86" t="s">
-        <v>452</v>
-      </c>
-      <c r="H86" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="87" spans="1:8">
+    <row r="87" spans="1:7">
       <c r="A87">
         <v>86</v>
       </c>
@@ -13818,20 +13569,17 @@
       <c r="C87">
         <v>13</v>
       </c>
-      <c r="D87">
-        <v>0</v>
-      </c>
-      <c r="E87" t="s">
+      <c r="D87" t="s">
         <v>375</v>
+      </c>
+      <c r="F87" t="s">
+        <v>494</v>
       </c>
       <c r="G87" t="s">
         <v>494</v>
       </c>
-      <c r="H87" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8">
+    </row>
+    <row r="88" spans="1:7">
       <c r="A88">
         <v>87</v>
       </c>
@@ -13841,20 +13589,17 @@
       <c r="C88">
         <v>14</v>
       </c>
-      <c r="D88">
-        <v>0</v>
-      </c>
-      <c r="E88" t="s">
+      <c r="D88" t="s">
         <v>376</v>
+      </c>
+      <c r="F88" t="s">
+        <v>494</v>
       </c>
       <c r="G88" t="s">
         <v>494</v>
       </c>
-      <c r="H88" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8">
+    </row>
+    <row r="89" spans="1:7">
       <c r="A89">
         <v>88</v>
       </c>
@@ -13864,20 +13609,17 @@
       <c r="C89">
         <v>15</v>
       </c>
-      <c r="D89">
-        <v>0</v>
-      </c>
-      <c r="E89" t="s">
+      <c r="D89" t="s">
         <v>377</v>
+      </c>
+      <c r="F89" t="s">
+        <v>494</v>
       </c>
       <c r="G89" t="s">
         <v>494</v>
       </c>
-      <c r="H89" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8">
+    </row>
+    <row r="90" spans="1:7">
       <c r="A90">
         <v>89</v>
       </c>
@@ -13887,20 +13629,17 @@
       <c r="C90">
         <v>16</v>
       </c>
-      <c r="D90">
-        <v>0</v>
-      </c>
-      <c r="E90" t="s">
+      <c r="D90" t="s">
         <v>378</v>
+      </c>
+      <c r="F90" t="s">
+        <v>494</v>
       </c>
       <c r="G90" t="s">
         <v>494</v>
       </c>
-      <c r="H90" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8">
+    </row>
+    <row r="91" spans="1:7">
       <c r="A91">
         <v>90</v>
       </c>
@@ -13910,23 +13649,20 @@
       <c r="C91">
         <v>17</v>
       </c>
-      <c r="D91">
-        <v>0</v>
-      </c>
-      <c r="E91" t="s">
+      <c r="D91" t="s">
         <v>92</v>
       </c>
-      <c r="F91" s="1" t="s">
+      <c r="E91" s="1" t="s">
         <v>495</v>
       </c>
+      <c r="F91" t="s">
+        <v>468</v>
+      </c>
       <c r="G91" t="s">
-        <v>468</v>
-      </c>
-      <c r="H91" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="92" spans="1:8">
+    <row r="92" spans="1:7">
       <c r="A92">
         <v>91</v>
       </c>
@@ -13936,20 +13672,17 @@
       <c r="C92">
         <v>18</v>
       </c>
-      <c r="D92">
-        <v>0</v>
-      </c>
-      <c r="E92" t="s">
+      <c r="D92" t="s">
         <v>97</v>
       </c>
+      <c r="F92" t="s">
+        <v>496</v>
+      </c>
       <c r="G92" t="s">
-        <v>496</v>
-      </c>
-      <c r="H92" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="93" spans="1:8">
+    <row r="93" spans="1:7">
       <c r="A93">
         <v>92</v>
       </c>
@@ -13959,23 +13692,20 @@
       <c r="C93">
         <v>19</v>
       </c>
-      <c r="D93">
-        <v>0</v>
+      <c r="D93" t="s">
+        <v>102</v>
       </c>
       <c r="E93" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F93" t="s">
-        <v>103</v>
+        <v>457</v>
       </c>
       <c r="G93" t="s">
-        <v>457</v>
-      </c>
-      <c r="H93" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="94" spans="1:8">
+    <row r="94" spans="1:7">
       <c r="A94">
         <v>93</v>
       </c>
@@ -13985,23 +13715,20 @@
       <c r="C94">
         <v>20</v>
       </c>
-      <c r="D94">
-        <v>0</v>
+      <c r="D94" t="s">
+        <v>107</v>
       </c>
       <c r="E94" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="F94" t="s">
-        <v>103</v>
+        <v>457</v>
       </c>
       <c r="G94" t="s">
-        <v>457</v>
-      </c>
-      <c r="H94" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="95" spans="1:8">
+    <row r="95" spans="1:7">
       <c r="A95">
         <v>94</v>
       </c>
@@ -14011,20 +13738,17 @@
       <c r="C95">
         <v>21</v>
       </c>
-      <c r="D95">
-        <v>0</v>
-      </c>
-      <c r="E95" t="s">
+      <c r="D95" t="s">
         <v>110</v>
       </c>
+      <c r="F95" t="s">
+        <v>497</v>
+      </c>
       <c r="G95" t="s">
-        <v>497</v>
-      </c>
-      <c r="H95" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="96" spans="1:8">
+    <row r="96" spans="1:7">
       <c r="A96">
         <v>95</v>
       </c>
@@ -14034,20 +13758,17 @@
       <c r="C96">
         <v>22</v>
       </c>
-      <c r="D96">
-        <v>0</v>
-      </c>
-      <c r="E96" t="s">
+      <c r="D96" t="s">
         <v>115</v>
       </c>
+      <c r="F96" t="s">
+        <v>498</v>
+      </c>
       <c r="G96" t="s">
-        <v>498</v>
-      </c>
-      <c r="H96" t="s">
         <v>499</v>
       </c>
     </row>
-    <row r="97" spans="1:8">
+    <row r="97" spans="1:7">
       <c r="A97">
         <v>96</v>
       </c>
@@ -14057,20 +13778,17 @@
       <c r="C97">
         <v>23</v>
       </c>
-      <c r="D97">
-        <v>0</v>
-      </c>
-      <c r="E97" t="s">
+      <c r="D97" t="s">
         <v>121</v>
       </c>
+      <c r="F97" t="s">
+        <v>498</v>
+      </c>
       <c r="G97" t="s">
-        <v>498</v>
-      </c>
-      <c r="H97" t="s">
         <v>499</v>
       </c>
     </row>
-    <row r="98" spans="1:8">
+    <row r="98" spans="1:7">
       <c r="A98">
         <v>97</v>
       </c>
@@ -14080,20 +13798,17 @@
       <c r="C98">
         <v>24</v>
       </c>
-      <c r="D98">
-        <v>0</v>
-      </c>
-      <c r="E98" t="s">
+      <c r="D98" t="s">
         <v>125</v>
       </c>
+      <c r="F98" t="s">
+        <v>498</v>
+      </c>
       <c r="G98" t="s">
-        <v>498</v>
-      </c>
-      <c r="H98" t="s">
         <v>499</v>
       </c>
     </row>
-    <row r="99" spans="1:8">
+    <row r="99" spans="1:7">
       <c r="A99">
         <v>98</v>
       </c>
@@ -14103,20 +13818,17 @@
       <c r="C99">
         <v>25</v>
       </c>
-      <c r="D99">
-        <v>0</v>
-      </c>
-      <c r="E99" t="s">
+      <c r="D99" t="s">
         <v>129</v>
       </c>
+      <c r="F99" t="s">
+        <v>498</v>
+      </c>
       <c r="G99" t="s">
-        <v>498</v>
-      </c>
-      <c r="H99" t="s">
         <v>499</v>
       </c>
     </row>
-    <row r="100" spans="1:8">
+    <row r="100" spans="1:7">
       <c r="A100">
         <v>99</v>
       </c>
@@ -14126,20 +13838,17 @@
       <c r="C100">
         <v>26</v>
       </c>
-      <c r="D100">
-        <v>0</v>
-      </c>
-      <c r="E100" t="s">
+      <c r="D100" t="s">
         <v>133</v>
       </c>
+      <c r="F100" t="s">
+        <v>461</v>
+      </c>
       <c r="G100" t="s">
-        <v>461</v>
-      </c>
-      <c r="H100" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="101" spans="1:8">
+    <row r="101" spans="1:7">
       <c r="A101">
         <v>100</v>
       </c>
@@ -14149,20 +13858,17 @@
       <c r="C101">
         <v>27</v>
       </c>
-      <c r="D101">
-        <v>0</v>
-      </c>
-      <c r="E101" t="s">
+      <c r="D101" t="s">
         <v>138</v>
       </c>
+      <c r="F101" t="s">
+        <v>461</v>
+      </c>
       <c r="G101" t="s">
-        <v>461</v>
-      </c>
-      <c r="H101" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="102" spans="1:8">
+    <row r="102" spans="1:7">
       <c r="A102">
         <v>101</v>
       </c>
@@ -14172,20 +13878,17 @@
       <c r="C102">
         <v>28</v>
       </c>
-      <c r="D102">
-        <v>0</v>
-      </c>
-      <c r="E102" t="s">
+      <c r="D102" t="s">
         <v>141</v>
       </c>
+      <c r="F102" t="s">
+        <v>461</v>
+      </c>
       <c r="G102" t="s">
-        <v>461</v>
-      </c>
-      <c r="H102" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="103" spans="1:8">
+    <row r="103" spans="1:7">
       <c r="A103">
         <v>102</v>
       </c>
@@ -14195,20 +13898,17 @@
       <c r="C103">
         <v>29</v>
       </c>
-      <c r="D103">
-        <v>0</v>
-      </c>
-      <c r="E103" t="s">
+      <c r="D103" t="s">
         <v>144</v>
       </c>
+      <c r="F103" t="s">
+        <v>461</v>
+      </c>
       <c r="G103" t="s">
-        <v>461</v>
-      </c>
-      <c r="H103" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="104" spans="1:8">
+    <row r="104" spans="1:7">
       <c r="A104">
         <v>103</v>
       </c>
@@ -14218,20 +13918,17 @@
       <c r="C104">
         <v>30</v>
       </c>
-      <c r="D104">
-        <v>0</v>
-      </c>
-      <c r="E104" t="s">
+      <c r="D104" t="s">
         <v>148</v>
       </c>
+      <c r="F104" t="s">
+        <v>461</v>
+      </c>
       <c r="G104" t="s">
-        <v>461</v>
-      </c>
-      <c r="H104" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="105" spans="1:8">
+    <row r="105" spans="1:7">
       <c r="A105">
         <v>104</v>
       </c>
@@ -14241,20 +13938,17 @@
       <c r="C105">
         <v>31</v>
       </c>
-      <c r="D105">
-        <v>0</v>
-      </c>
-      <c r="E105" t="s">
+      <c r="D105" t="s">
         <v>151</v>
       </c>
+      <c r="F105" t="s">
+        <v>501</v>
+      </c>
       <c r="G105" t="s">
-        <v>501</v>
-      </c>
-      <c r="H105" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="106" spans="1:8">
+    <row r="106" spans="1:7">
       <c r="A106">
         <v>105</v>
       </c>
@@ -14264,20 +13958,17 @@
       <c r="C106">
         <v>32</v>
       </c>
-      <c r="D106">
-        <v>0</v>
-      </c>
-      <c r="E106" t="s">
+      <c r="D106" t="s">
         <v>156</v>
       </c>
+      <c r="F106" t="s">
+        <v>501</v>
+      </c>
       <c r="G106" t="s">
-        <v>501</v>
-      </c>
-      <c r="H106" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="107" spans="1:8">
+    <row r="107" spans="1:7">
       <c r="A107">
         <v>106</v>
       </c>
@@ -14287,20 +13978,17 @@
       <c r="C107">
         <v>33</v>
       </c>
-      <c r="D107">
-        <v>0</v>
-      </c>
-      <c r="E107" t="s">
+      <c r="D107" t="s">
         <v>159</v>
       </c>
+      <c r="F107" t="s">
+        <v>503</v>
+      </c>
       <c r="G107" t="s">
-        <v>503</v>
-      </c>
-      <c r="H107" t="s">
         <v>504</v>
       </c>
     </row>
-    <row r="108" spans="1:8">
+    <row r="108" spans="1:7">
       <c r="A108">
         <v>107</v>
       </c>
@@ -14310,20 +13998,17 @@
       <c r="C108">
         <v>34</v>
       </c>
-      <c r="D108">
-        <v>0</v>
-      </c>
-      <c r="E108" t="s">
+      <c r="D108" t="s">
         <v>163</v>
       </c>
+      <c r="F108" t="s">
+        <v>503</v>
+      </c>
       <c r="G108" t="s">
-        <v>503</v>
-      </c>
-      <c r="H108" t="s">
         <v>504</v>
       </c>
     </row>
-    <row r="109" spans="1:9">
+    <row r="109" spans="1:8">
       <c r="A109">
         <v>108</v>
       </c>
@@ -14333,26 +14018,23 @@
       <c r="C109">
         <v>35</v>
       </c>
-      <c r="D109">
-        <v>0</v>
-      </c>
-      <c r="E109" t="s">
+      <c r="D109" t="s">
         <v>166</v>
       </c>
-      <c r="F109" s="1" t="s">
+      <c r="E109" s="1" t="s">
         <v>505</v>
       </c>
+      <c r="F109" t="s">
+        <v>506</v>
+      </c>
       <c r="G109" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H109" t="s">
-        <v>507</v>
-      </c>
-      <c r="I109" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="110" spans="1:9">
+    <row r="110" spans="1:8">
       <c r="A110">
         <v>109</v>
       </c>
@@ -14362,26 +14044,23 @@
       <c r="C110">
         <v>36</v>
       </c>
-      <c r="D110">
-        <v>0</v>
-      </c>
-      <c r="E110" t="s">
+      <c r="D110" t="s">
         <v>170</v>
       </c>
-      <c r="F110" s="1" t="s">
+      <c r="E110" s="1" t="s">
         <v>508</v>
       </c>
+      <c r="F110" t="s">
+        <v>509</v>
+      </c>
       <c r="G110" t="s">
-        <v>509</v>
+        <v>460</v>
       </c>
       <c r="H110" t="s">
-        <v>460</v>
-      </c>
-      <c r="I110" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="111" spans="1:9">
+    <row r="111" spans="1:8">
       <c r="A111">
         <v>110</v>
       </c>
@@ -14391,26 +14070,23 @@
       <c r="C111">
         <v>37</v>
       </c>
-      <c r="D111">
-        <v>0</v>
-      </c>
-      <c r="E111" t="s">
+      <c r="D111" t="s">
         <v>174</v>
       </c>
-      <c r="F111" s="1" t="s">
+      <c r="E111" s="1" t="s">
         <v>508</v>
       </c>
+      <c r="F111" t="s">
+        <v>506</v>
+      </c>
       <c r="G111" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H111" t="s">
-        <v>507</v>
-      </c>
-      <c r="I111" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="112" spans="1:9">
+    <row r="112" spans="1:8">
       <c r="A112">
         <v>111</v>
       </c>
@@ -14420,26 +14096,23 @@
       <c r="C112">
         <v>38</v>
       </c>
-      <c r="D112">
-        <v>0</v>
-      </c>
-      <c r="E112" t="s">
+      <c r="D112" t="s">
         <v>177</v>
       </c>
-      <c r="F112" s="1" t="s">
+      <c r="E112" s="1" t="s">
         <v>508</v>
       </c>
+      <c r="F112" t="s">
+        <v>509</v>
+      </c>
       <c r="G112" t="s">
-        <v>509</v>
+        <v>460</v>
       </c>
       <c r="H112" t="s">
-        <v>460</v>
-      </c>
-      <c r="I112" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="113" spans="1:8">
+    <row r="113" spans="1:7">
       <c r="A113">
         <v>112</v>
       </c>
@@ -14449,23 +14122,20 @@
       <c r="C113">
         <v>39</v>
       </c>
-      <c r="D113">
-        <v>0</v>
+      <c r="D113" t="s">
+        <v>180</v>
       </c>
       <c r="E113" t="s">
-        <v>180</v>
+        <v>31</v>
       </c>
       <c r="F113" t="s">
-        <v>31</v>
+        <v>461</v>
       </c>
       <c r="G113" t="s">
-        <v>461</v>
-      </c>
-      <c r="H113" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="114" spans="1:8">
+    <row r="114" spans="1:7">
       <c r="A114">
         <v>113</v>
       </c>
@@ -14475,23 +14145,20 @@
       <c r="C114">
         <v>40</v>
       </c>
-      <c r="D114">
-        <v>0</v>
+      <c r="D114" t="s">
+        <v>183</v>
       </c>
       <c r="E114" t="s">
-        <v>183</v>
+        <v>19</v>
       </c>
       <c r="F114" t="s">
-        <v>19</v>
+        <v>461</v>
       </c>
       <c r="G114" t="s">
-        <v>461</v>
-      </c>
-      <c r="H114" t="s">
         <v>511</v>
       </c>
     </row>
-    <row r="115" spans="1:8">
+    <row r="115" spans="1:7">
       <c r="A115">
         <v>114</v>
       </c>
@@ -14501,20 +14168,17 @@
       <c r="C115">
         <v>41</v>
       </c>
-      <c r="D115">
-        <v>0</v>
-      </c>
-      <c r="E115" t="s">
+      <c r="D115" t="s">
         <v>404</v>
+      </c>
+      <c r="F115" t="s">
+        <v>468</v>
       </c>
       <c r="G115" t="s">
         <v>468</v>
       </c>
-      <c r="H115" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="116" spans="1:8">
+    </row>
+    <row r="116" spans="1:7">
       <c r="A116">
         <v>115</v>
       </c>
@@ -14524,20 +14188,17 @@
       <c r="C116">
         <v>42</v>
       </c>
-      <c r="D116">
-        <v>0</v>
-      </c>
-      <c r="E116" t="s">
+      <c r="D116" t="s">
         <v>405</v>
+      </c>
+      <c r="F116" t="s">
+        <v>468</v>
       </c>
       <c r="G116" t="s">
         <v>468</v>
       </c>
-      <c r="H116" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="117" spans="1:8">
+    </row>
+    <row r="117" spans="1:7">
       <c r="A117">
         <v>116</v>
       </c>
@@ -14547,23 +14208,20 @@
       <c r="C117">
         <v>43</v>
       </c>
-      <c r="D117">
-        <v>0</v>
-      </c>
-      <c r="E117" t="s">
+      <c r="D117" t="s">
         <v>194</v>
       </c>
-      <c r="F117" s="1" t="s">
+      <c r="E117" s="1" t="s">
         <v>512</v>
       </c>
+      <c r="F117" t="s">
+        <v>468</v>
+      </c>
       <c r="G117" t="s">
-        <v>468</v>
-      </c>
-      <c r="H117" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="118" spans="1:8">
+    <row r="118" spans="1:7">
       <c r="A118">
         <v>117</v>
       </c>
@@ -14573,23 +14231,20 @@
       <c r="C118">
         <v>44</v>
       </c>
-      <c r="D118">
-        <v>0</v>
-      </c>
-      <c r="E118" t="s">
+      <c r="D118" t="s">
         <v>198</v>
       </c>
-      <c r="F118" s="1" t="s">
+      <c r="E118" s="1" t="s">
         <v>512</v>
       </c>
+      <c r="F118" t="s">
+        <v>468</v>
+      </c>
       <c r="G118" t="s">
-        <v>468</v>
-      </c>
-      <c r="H118" t="s">
         <v>514</v>
       </c>
     </row>
-    <row r="119" spans="1:8">
+    <row r="119" spans="1:7">
       <c r="A119">
         <v>118</v>
       </c>
@@ -14599,23 +14254,20 @@
       <c r="C119">
         <v>45</v>
       </c>
-      <c r="D119">
-        <v>0</v>
-      </c>
-      <c r="E119" t="s">
+      <c r="D119" t="s">
         <v>202</v>
       </c>
-      <c r="F119" s="1" t="s">
+      <c r="E119" s="1" t="s">
         <v>512</v>
       </c>
+      <c r="F119" t="s">
+        <v>468</v>
+      </c>
       <c r="G119" t="s">
-        <v>468</v>
-      </c>
-      <c r="H119" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="120" spans="1:8">
+    <row r="120" spans="1:7">
       <c r="A120">
         <v>119</v>
       </c>
@@ -14625,23 +14277,20 @@
       <c r="C120">
         <v>46</v>
       </c>
-      <c r="D120">
-        <v>0</v>
-      </c>
-      <c r="E120" t="s">
+      <c r="D120" t="s">
         <v>206</v>
       </c>
-      <c r="F120" s="1" t="s">
+      <c r="E120" s="1" t="s">
         <v>512</v>
       </c>
+      <c r="F120" t="s">
+        <v>468</v>
+      </c>
       <c r="G120" t="s">
-        <v>468</v>
-      </c>
-      <c r="H120" t="s">
         <v>514</v>
       </c>
     </row>
-    <row r="121" spans="1:8">
+    <row r="121" spans="1:7">
       <c r="A121">
         <v>120</v>
       </c>
@@ -14651,23 +14300,20 @@
       <c r="C121">
         <v>47</v>
       </c>
-      <c r="D121">
-        <v>0</v>
-      </c>
-      <c r="E121" t="s">
+      <c r="D121" t="s">
         <v>209</v>
       </c>
-      <c r="F121" s="1" t="s">
+      <c r="E121" s="1" t="s">
         <v>512</v>
       </c>
+      <c r="F121" t="s">
+        <v>468</v>
+      </c>
       <c r="G121" t="s">
-        <v>468</v>
-      </c>
-      <c r="H121" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="122" spans="1:8">
+    <row r="122" spans="1:7">
       <c r="A122">
         <v>121</v>
       </c>
@@ -14677,23 +14323,20 @@
       <c r="C122">
         <v>48</v>
       </c>
-      <c r="D122">
-        <v>0</v>
+      <c r="D122" t="s">
+        <v>212</v>
       </c>
       <c r="E122" t="s">
-        <v>212</v>
+        <v>303</v>
       </c>
       <c r="F122" t="s">
-        <v>303</v>
+        <v>516</v>
       </c>
       <c r="G122" t="s">
-        <v>516</v>
-      </c>
-      <c r="H122" t="s">
         <v>517</v>
       </c>
     </row>
-    <row r="123" spans="1:8">
+    <row r="123" spans="1:7">
       <c r="A123">
         <v>122</v>
       </c>
@@ -14703,23 +14346,20 @@
       <c r="C123">
         <v>49</v>
       </c>
-      <c r="D123">
-        <v>0</v>
+      <c r="D123" t="s">
+        <v>216</v>
       </c>
       <c r="E123" t="s">
-        <v>216</v>
+        <v>303</v>
       </c>
       <c r="F123" t="s">
-        <v>303</v>
+        <v>516</v>
       </c>
       <c r="G123" t="s">
-        <v>516</v>
-      </c>
-      <c r="H123" t="s">
         <v>517</v>
       </c>
     </row>
-    <row r="124" spans="1:8">
+    <row r="124" spans="1:7">
       <c r="A124">
         <v>123</v>
       </c>
@@ -14729,20 +14369,17 @@
       <c r="C124">
         <v>50</v>
       </c>
-      <c r="D124">
-        <v>0</v>
-      </c>
-      <c r="E124" t="s">
+      <c r="D124" t="s">
         <v>219</v>
+      </c>
+      <c r="F124" t="s">
+        <v>468</v>
       </c>
       <c r="G124" t="s">
         <v>468</v>
       </c>
-      <c r="H124" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="125" spans="1:8">
+    </row>
+    <row r="125" spans="1:7">
       <c r="A125">
         <v>124</v>
       </c>
@@ -14752,20 +14389,17 @@
       <c r="C125">
         <v>51</v>
       </c>
-      <c r="D125">
-        <v>0</v>
-      </c>
-      <c r="E125" t="s">
+      <c r="D125" t="s">
         <v>222</v>
+      </c>
+      <c r="F125" t="s">
+        <v>468</v>
       </c>
       <c r="G125" t="s">
         <v>468</v>
       </c>
-      <c r="H125" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="126" spans="1:8">
+    </row>
+    <row r="126" spans="1:7">
       <c r="A126">
         <v>125</v>
       </c>
@@ -14775,20 +14409,17 @@
       <c r="C126">
         <v>52</v>
       </c>
-      <c r="D126">
-        <v>0</v>
-      </c>
-      <c r="E126" s="2" t="s">
+      <c r="D126" s="2" t="s">
         <v>518</v>
+      </c>
+      <c r="F126" t="s">
+        <v>468</v>
       </c>
       <c r="G126" t="s">
         <v>468</v>
       </c>
-      <c r="H126" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="127" spans="1:8">
+    </row>
+    <row r="127" spans="1:7">
       <c r="A127">
         <v>126</v>
       </c>
@@ -14798,20 +14429,17 @@
       <c r="C127">
         <v>53</v>
       </c>
-      <c r="D127">
-        <v>0</v>
-      </c>
-      <c r="E127" t="s">
+      <c r="D127" t="s">
         <v>230</v>
+      </c>
+      <c r="F127" t="s">
+        <v>468</v>
       </c>
       <c r="G127" t="s">
         <v>468</v>
       </c>
-      <c r="H127" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="128" spans="1:8">
+    </row>
+    <row r="128" spans="1:7">
       <c r="A128">
         <v>127</v>
       </c>
@@ -14821,20 +14449,17 @@
       <c r="C128">
         <v>54</v>
       </c>
-      <c r="D128">
-        <v>0</v>
-      </c>
-      <c r="E128" t="s">
+      <c r="D128" t="s">
         <v>310</v>
+      </c>
+      <c r="F128" t="s">
+        <v>468</v>
       </c>
       <c r="G128" t="s">
         <v>468</v>
       </c>
-      <c r="H128" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="129" spans="1:8">
+    </row>
+    <row r="129" spans="1:7">
       <c r="A129">
         <v>128</v>
       </c>
@@ -14844,23 +14469,20 @@
       <c r="C129">
         <v>55</v>
       </c>
-      <c r="D129">
-        <v>0</v>
+      <c r="D129" t="s">
+        <v>312</v>
       </c>
       <c r="E129" t="s">
-        <v>312</v>
+        <v>411</v>
       </c>
       <c r="F129" t="s">
-        <v>411</v>
+        <v>468</v>
       </c>
       <c r="G129" t="s">
-        <v>468</v>
-      </c>
-      <c r="H129" t="s">
         <v>519</v>
       </c>
     </row>
-    <row r="130" spans="1:9">
+    <row r="130" spans="1:8">
       <c r="A130">
         <v>129</v>
       </c>
@@ -14870,23 +14492,20 @@
       <c r="C130">
         <v>56</v>
       </c>
-      <c r="D130">
-        <v>0</v>
+      <c r="D130" t="s">
+        <v>316</v>
       </c>
       <c r="E130" t="s">
-        <v>316</v>
-      </c>
-      <c r="F130" t="s">
         <v>520</v>
       </c>
-      <c r="H130" t="s">
+      <c r="G130" t="s">
         <v>520</v>
       </c>
-      <c r="I130" s="2" t="s">
+      <c r="H130" s="2" t="s">
         <v>521</v>
       </c>
     </row>
-    <row r="131" spans="1:8">
+    <row r="131" spans="1:7">
       <c r="A131">
         <v>130</v>
       </c>
@@ -14896,20 +14515,17 @@
       <c r="C131">
         <v>57</v>
       </c>
-      <c r="D131">
-        <v>0</v>
-      </c>
-      <c r="E131" t="s">
+      <c r="D131" t="s">
         <v>320</v>
+      </c>
+      <c r="F131" t="s">
+        <v>468</v>
       </c>
       <c r="G131" t="s">
         <v>468</v>
       </c>
-      <c r="H131" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="132" spans="1:8">
+    </row>
+    <row r="132" spans="1:7">
       <c r="A132">
         <v>131</v>
       </c>
@@ -14919,20 +14535,17 @@
       <c r="C132">
         <v>58</v>
       </c>
-      <c r="D132">
-        <v>0</v>
-      </c>
-      <c r="E132" t="s">
+      <c r="D132" t="s">
         <v>323</v>
+      </c>
+      <c r="F132" t="s">
+        <v>468</v>
       </c>
       <c r="G132" t="s">
         <v>468</v>
       </c>
-      <c r="H132" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="133" spans="1:8">
+    </row>
+    <row r="133" spans="1:7">
       <c r="A133">
         <v>132</v>
       </c>
@@ -14942,23 +14555,20 @@
       <c r="C133">
         <v>59</v>
       </c>
-      <c r="D133">
-        <v>0</v>
+      <c r="D133" t="s">
+        <v>325</v>
       </c>
       <c r="E133" t="s">
-        <v>325</v>
+        <v>415</v>
       </c>
       <c r="F133" t="s">
-        <v>415</v>
+        <v>468</v>
       </c>
       <c r="G133" t="s">
         <v>468</v>
       </c>
-      <c r="H133" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="134" spans="1:8">
+    </row>
+    <row r="134" spans="1:7">
       <c r="A134">
         <v>133</v>
       </c>
@@ -14968,20 +14578,17 @@
       <c r="C134">
         <v>60</v>
       </c>
-      <c r="D134">
-        <v>0</v>
-      </c>
-      <c r="E134" s="1" t="s">
+      <c r="D134" s="1" t="s">
         <v>416</v>
       </c>
+      <c r="F134" t="s">
+        <v>522</v>
+      </c>
       <c r="G134" t="s">
-        <v>522</v>
-      </c>
-      <c r="H134" t="s">
         <v>523</v>
       </c>
     </row>
-    <row r="135" spans="1:8">
+    <row r="135" spans="1:7">
       <c r="A135">
         <v>134</v>
       </c>
@@ -14991,23 +14598,20 @@
       <c r="C135">
         <v>61</v>
       </c>
-      <c r="D135">
-        <v>0</v>
+      <c r="D135" t="s">
+        <v>331</v>
       </c>
       <c r="E135" t="s">
-        <v>331</v>
+        <v>415</v>
       </c>
       <c r="F135" t="s">
-        <v>415</v>
+        <v>468</v>
       </c>
       <c r="G135" t="s">
         <v>468</v>
       </c>
-      <c r="H135" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="136" spans="1:8">
+    </row>
+    <row r="136" spans="1:7">
       <c r="A136">
         <v>135</v>
       </c>
@@ -15017,23 +14621,20 @@
       <c r="C136">
         <v>62</v>
       </c>
-      <c r="D136">
-        <v>0</v>
+      <c r="D136" t="s">
+        <v>333</v>
       </c>
       <c r="E136" t="s">
-        <v>333</v>
+        <v>415</v>
       </c>
       <c r="F136" t="s">
-        <v>415</v>
+        <v>468</v>
       </c>
       <c r="G136" t="s">
         <v>468</v>
       </c>
-      <c r="H136" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="137" spans="1:8">
+    </row>
+    <row r="137" spans="1:7">
       <c r="A137">
         <v>136</v>
       </c>
@@ -15043,23 +14644,20 @@
       <c r="C137">
         <v>63</v>
       </c>
-      <c r="D137">
-        <v>0</v>
+      <c r="D137" t="s">
+        <v>335</v>
       </c>
       <c r="E137" t="s">
-        <v>335</v>
+        <v>103</v>
       </c>
       <c r="F137" t="s">
-        <v>103</v>
+        <v>457</v>
       </c>
       <c r="G137" t="s">
-        <v>457</v>
-      </c>
-      <c r="H137" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="138" spans="1:8">
+    <row r="138" spans="1:7">
       <c r="A138">
         <v>137</v>
       </c>
@@ -15069,23 +14667,20 @@
       <c r="C138">
         <v>64</v>
       </c>
-      <c r="D138">
-        <v>0</v>
+      <c r="D138" t="s">
+        <v>337</v>
       </c>
       <c r="E138" t="s">
-        <v>337</v>
+        <v>103</v>
       </c>
       <c r="F138" t="s">
-        <v>103</v>
+        <v>457</v>
       </c>
       <c r="G138" t="s">
-        <v>457</v>
-      </c>
-      <c r="H138" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="139" spans="1:8">
+    <row r="139" spans="1:7">
       <c r="A139">
         <v>138</v>
       </c>
@@ -15095,20 +14690,17 @@
       <c r="C139">
         <v>65</v>
       </c>
-      <c r="D139">
-        <v>0</v>
-      </c>
-      <c r="E139" t="s">
+      <c r="D139" t="s">
         <v>339</v>
       </c>
+      <c r="F139" t="s">
+        <v>468</v>
+      </c>
       <c r="G139" t="s">
-        <v>468</v>
-      </c>
-      <c r="H139" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="140" spans="1:8">
+    <row r="140" spans="1:7">
       <c r="A140">
         <v>139</v>
       </c>
@@ -15118,20 +14710,17 @@
       <c r="C140">
         <v>66</v>
       </c>
-      <c r="D140">
-        <v>0</v>
-      </c>
-      <c r="E140" t="s">
+      <c r="D140" t="s">
         <v>341</v>
       </c>
+      <c r="F140" t="s">
+        <v>457</v>
+      </c>
       <c r="G140" t="s">
-        <v>457</v>
-      </c>
-      <c r="H140" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="141" spans="1:8">
+    <row r="141" spans="1:7">
       <c r="A141">
         <v>140</v>
       </c>
@@ -15141,20 +14730,17 @@
       <c r="C141">
         <v>67</v>
       </c>
-      <c r="D141">
-        <v>0</v>
-      </c>
-      <c r="E141" t="s">
+      <c r="D141" t="s">
         <v>321</v>
+      </c>
+      <c r="F141" t="s">
+        <v>468</v>
       </c>
       <c r="G141" t="s">
         <v>468</v>
       </c>
-      <c r="H141" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="142" spans="1:8">
+    </row>
+    <row r="142" spans="1:7">
       <c r="A142">
         <v>141</v>
       </c>
@@ -15164,23 +14750,20 @@
       <c r="C142">
         <v>68</v>
       </c>
-      <c r="D142">
-        <v>0</v>
-      </c>
-      <c r="E142" s="2" t="s">
+      <c r="D142" s="2" t="s">
         <v>524</v>
       </c>
+      <c r="E142" t="s">
+        <v>421</v>
+      </c>
       <c r="F142" t="s">
-        <v>421</v>
+        <v>525</v>
       </c>
       <c r="G142" t="s">
-        <v>525</v>
-      </c>
-      <c r="H142" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="143" spans="1:8">
+    <row r="143" spans="1:7">
       <c r="A143">
         <v>142</v>
       </c>
@@ -15190,23 +14773,20 @@
       <c r="C143">
         <v>69</v>
       </c>
-      <c r="D143">
-        <v>0</v>
-      </c>
-      <c r="E143" s="2" t="s">
+      <c r="D143" s="2" t="s">
         <v>527</v>
       </c>
-      <c r="F143" s="1" t="s">
+      <c r="E143" s="1" t="s">
         <v>512</v>
       </c>
+      <c r="F143" t="s">
+        <v>468</v>
+      </c>
       <c r="G143" t="s">
-        <v>468</v>
-      </c>
-      <c r="H143" t="s">
         <v>528</v>
       </c>
     </row>
-    <row r="144" spans="1:8">
+    <row r="144" spans="1:7">
       <c r="A144">
         <v>143</v>
       </c>
@@ -15216,23 +14796,20 @@
       <c r="C144">
         <v>70</v>
       </c>
-      <c r="D144">
-        <v>0</v>
+      <c r="D144" t="s">
+        <v>427</v>
       </c>
       <c r="E144" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F144" t="s">
-        <v>428</v>
+        <v>529</v>
       </c>
       <c r="G144" t="s">
-        <v>529</v>
-      </c>
-      <c r="H144" t="s">
         <v>530</v>
       </c>
     </row>
-    <row r="145" spans="1:9">
+    <row r="145" spans="1:8">
       <c r="A145">
         <v>144</v>
       </c>
@@ -15242,23 +14819,20 @@
       <c r="C145">
         <v>71</v>
       </c>
-      <c r="D145">
-        <v>0</v>
-      </c>
-      <c r="E145" t="s">
+      <c r="D145" t="s">
         <v>431</v>
       </c>
-      <c r="F145" s="1" t="s">
+      <c r="E145" s="1" t="s">
         <v>531</v>
       </c>
-      <c r="H145" s="1" t="s">
+      <c r="G145" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="I145" t="s">
+      <c r="H145" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="146" spans="1:9">
+    <row r="146" spans="1:8">
       <c r="A146">
         <v>145</v>
       </c>
@@ -15268,23 +14842,20 @@
       <c r="C146">
         <v>72</v>
       </c>
-      <c r="D146">
-        <v>0</v>
-      </c>
-      <c r="E146" t="s">
+      <c r="D146" t="s">
         <v>436</v>
       </c>
-      <c r="F146" s="1" t="s">
+      <c r="E146" s="1" t="s">
         <v>531</v>
       </c>
-      <c r="H146" s="1" t="s">
+      <c r="G146" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="I146" t="s">
+      <c r="H146" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="147" spans="1:9">
+    <row r="147" spans="1:8">
       <c r="A147">
         <v>146</v>
       </c>
@@ -15294,23 +14865,20 @@
       <c r="C147">
         <v>73</v>
       </c>
-      <c r="D147">
-        <v>0</v>
-      </c>
-      <c r="E147" t="s">
+      <c r="D147" t="s">
         <v>438</v>
       </c>
-      <c r="F147" s="1" t="s">
+      <c r="E147" s="1" t="s">
         <v>531</v>
       </c>
-      <c r="H147" s="1" t="s">
+      <c r="G147" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="I147" t="s">
+      <c r="H147" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="148" spans="1:9">
+    <row r="148" spans="1:8">
       <c r="A148">
         <v>147</v>
       </c>
@@ -15320,23 +14888,20 @@
       <c r="C148">
         <v>74</v>
       </c>
-      <c r="D148">
-        <v>0</v>
-      </c>
-      <c r="E148" t="s">
+      <c r="D148" t="s">
         <v>440</v>
       </c>
-      <c r="F148" s="1" t="s">
+      <c r="E148" s="1" t="s">
         <v>531</v>
       </c>
-      <c r="H148" s="1" t="s">
+      <c r="G148" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="I148" t="s">
+      <c r="H148" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="149" spans="1:8">
+    <row r="149" spans="1:7">
       <c r="A149">
         <v>148</v>
       </c>
@@ -15346,17 +14911,14 @@
       <c r="C149">
         <v>128</v>
       </c>
-      <c r="D149">
-        <v>0</v>
-      </c>
-      <c r="E149" t="s">
+      <c r="D149" t="s">
         <v>351</v>
       </c>
-      <c r="H149" t="s">
+      <c r="G149" t="s">
         <v>533</v>
       </c>
     </row>
-    <row r="150" spans="1:8">
+    <row r="150" spans="1:7">
       <c r="A150">
         <v>149</v>
       </c>
@@ -15366,17 +14928,14 @@
       <c r="C150">
         <v>129</v>
       </c>
-      <c r="D150">
-        <v>0</v>
-      </c>
-      <c r="E150" t="s">
+      <c r="D150" t="s">
         <v>354</v>
       </c>
-      <c r="H150" t="s">
+      <c r="G150" t="s">
         <v>533</v>
       </c>
     </row>
-    <row r="151" spans="1:8">
+    <row r="151" spans="1:7">
       <c r="A151">
         <v>150</v>
       </c>
@@ -15386,17 +14945,14 @@
       <c r="C151">
         <v>130</v>
       </c>
-      <c r="D151">
-        <v>0</v>
-      </c>
-      <c r="E151" t="s">
+      <c r="D151" t="s">
         <v>356</v>
       </c>
-      <c r="H151" t="s">
+      <c r="G151" t="s">
         <v>533</v>
       </c>
     </row>
-    <row r="152" spans="1:8">
+    <row r="152" spans="1:7">
       <c r="A152">
         <v>151</v>
       </c>
@@ -15406,13 +14962,10 @@
       <c r="C152">
         <v>131</v>
       </c>
-      <c r="D152">
-        <v>0</v>
-      </c>
-      <c r="E152" t="s">
+      <c r="D152" t="s">
         <v>358</v>
       </c>
-      <c r="H152" t="s">
+      <c r="G152" t="s">
         <v>533</v>
       </c>
     </row>
